--- a/CarCar_Brain/bfs_tool/Carcar_Performance_Report.xlsx
+++ b/CarCar_Brain/bfs_tool/Carcar_Performance_Report.xlsx
@@ -414,7 +414,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G81"/>
+  <dimension ref="A1:G156"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -489,23 +489,23 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>Track_200</t>
+          <t>Track_Accel</t>
         </is>
       </c>
       <c r="C3" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="D3" t="n">
-        <v>0</v>
+        <v>1109</v>
       </c>
       <c r="E3" t="n">
-        <v>0</v>
+        <v>619</v>
       </c>
       <c r="F3" t="n">
-        <v>0</v>
+        <v>490</v>
       </c>
       <c r="G3" t="n">
-        <v>0</v>
+        <v>554</v>
       </c>
     </row>
     <row r="4">
@@ -516,23 +516,23 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>Track_Accel</t>
+          <t>Track_Decel</t>
         </is>
       </c>
       <c r="C4" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="D4" t="n">
-        <v>1109</v>
+        <v>1831</v>
       </c>
       <c r="E4" t="n">
-        <v>619</v>
+        <v>645</v>
       </c>
       <c r="F4" t="n">
-        <v>490</v>
+        <v>568</v>
       </c>
       <c r="G4" t="n">
-        <v>554</v>
+        <v>610</v>
       </c>
     </row>
     <row r="5">
@@ -543,23 +543,23 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>Track_Decel</t>
+          <t>Track_UTurn_in</t>
         </is>
       </c>
       <c r="C5" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="D5" t="n">
-        <v>1831</v>
+        <v>2296</v>
       </c>
       <c r="E5" t="n">
-        <v>645</v>
+        <v>573</v>
       </c>
       <c r="F5" t="n">
-        <v>568</v>
+        <v>391</v>
       </c>
       <c r="G5" t="n">
-        <v>610</v>
+        <v>459</v>
       </c>
     </row>
     <row r="6">
@@ -570,23 +570,23 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>Track_UTurn_in</t>
+          <t>Track_UTurn_out</t>
         </is>
       </c>
       <c r="C6" t="n">
-        <v>5</v>
+        <v>2</v>
       </c>
       <c r="D6" t="n">
-        <v>2296</v>
+        <v>857</v>
       </c>
       <c r="E6" t="n">
-        <v>573</v>
+        <v>438</v>
       </c>
       <c r="F6" t="n">
-        <v>391</v>
+        <v>419</v>
       </c>
       <c r="G6" t="n">
-        <v>459</v>
+        <v>428</v>
       </c>
     </row>
     <row r="7">
@@ -597,23 +597,23 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>Track_UTurn_out</t>
+          <t>Turn_F</t>
         </is>
       </c>
       <c r="C7" t="n">
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="D7" t="n">
-        <v>857</v>
+        <v>956</v>
       </c>
       <c r="E7" t="n">
-        <v>438</v>
+        <v>233</v>
       </c>
       <c r="F7" t="n">
-        <v>419</v>
+        <v>129</v>
       </c>
       <c r="G7" t="n">
-        <v>428</v>
+        <v>191</v>
       </c>
     </row>
     <row r="8">
@@ -624,23 +624,23 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>Turn_F</t>
+          <t>Turn_L</t>
         </is>
       </c>
       <c r="C8" t="n">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="D8" t="n">
-        <v>956</v>
+        <v>540</v>
       </c>
       <c r="E8" t="n">
-        <v>233</v>
+        <v>540</v>
       </c>
       <c r="F8" t="n">
-        <v>129</v>
+        <v>540</v>
       </c>
       <c r="G8" t="n">
-        <v>191</v>
+        <v>540</v>
       </c>
     </row>
     <row r="9">
@@ -651,23 +651,23 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>Turn_L</t>
+          <t>Turn_R</t>
         </is>
       </c>
       <c r="C9" t="n">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="D9" t="n">
-        <v>540</v>
+        <v>2290</v>
       </c>
       <c r="E9" t="n">
-        <v>540</v>
+        <v>489</v>
       </c>
       <c r="F9" t="n">
-        <v>540</v>
+        <v>386</v>
       </c>
       <c r="G9" t="n">
-        <v>540</v>
+        <v>458</v>
       </c>
     </row>
     <row r="10">
@@ -678,23 +678,23 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>Turn_R</t>
+          <t>Turn_B</t>
         </is>
       </c>
       <c r="C10" t="n">
-        <v>5</v>
+        <v>2</v>
       </c>
       <c r="D10" t="n">
-        <v>2290</v>
+        <v>2010</v>
       </c>
       <c r="E10" t="n">
-        <v>489</v>
+        <v>1034</v>
       </c>
       <c r="F10" t="n">
-        <v>386</v>
+        <v>976</v>
       </c>
       <c r="G10" t="n">
-        <v>458</v>
+        <v>1005</v>
       </c>
     </row>
     <row r="11">
@@ -705,23 +705,23 @@
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>Turn_B</t>
+          <t>Turn_T</t>
         </is>
       </c>
       <c r="C11" t="n">
         <v>2</v>
       </c>
       <c r="D11" t="n">
-        <v>2010</v>
+        <v>1574</v>
       </c>
       <c r="E11" t="n">
-        <v>1034</v>
+        <v>796</v>
       </c>
       <c r="F11" t="n">
-        <v>976</v>
+        <v>778</v>
       </c>
       <c r="G11" t="n">
-        <v>1005</v>
+        <v>787</v>
       </c>
     </row>
     <row r="12">
@@ -732,23 +732,23 @@
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>Turn_T</t>
+          <t>Turn_LB</t>
         </is>
       </c>
       <c r="C12" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="D12" t="n">
-        <v>1574</v>
+        <v>488</v>
       </c>
       <c r="E12" t="n">
-        <v>796</v>
+        <v>488</v>
       </c>
       <c r="F12" t="n">
-        <v>778</v>
+        <v>488</v>
       </c>
       <c r="G12" t="n">
-        <v>787</v>
+        <v>488</v>
       </c>
     </row>
     <row r="13">
@@ -759,50 +759,50 @@
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>Turn_LB</t>
+          <t>Turn_RB</t>
         </is>
       </c>
       <c r="C13" t="n">
         <v>1</v>
       </c>
       <c r="D13" t="n">
-        <v>488</v>
+        <v>489</v>
       </c>
       <c r="E13" t="n">
-        <v>488</v>
+        <v>489</v>
       </c>
       <c r="F13" t="n">
-        <v>488</v>
+        <v>489</v>
       </c>
       <c r="G13" t="n">
-        <v>488</v>
+        <v>489</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>Run_1</t>
+          <t>Run_2</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>Turn_RB</t>
+          <t>Track_150</t>
         </is>
       </c>
       <c r="C14" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="D14" t="n">
-        <v>489</v>
+        <v>1780</v>
       </c>
       <c r="E14" t="n">
-        <v>489</v>
+        <v>671</v>
       </c>
       <c r="F14" t="n">
-        <v>489</v>
+        <v>542</v>
       </c>
       <c r="G14" t="n">
-        <v>489</v>
+        <v>593</v>
       </c>
     </row>
     <row r="15">
@@ -813,20 +813,20 @@
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>Track_150</t>
+          <t>Track_Accel</t>
         </is>
       </c>
       <c r="C15" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="D15" t="n">
-        <v>1780</v>
+        <v>1186</v>
       </c>
       <c r="E15" t="n">
-        <v>671</v>
+        <v>645</v>
       </c>
       <c r="F15" t="n">
-        <v>542</v>
+        <v>541</v>
       </c>
       <c r="G15" t="n">
         <v>593</v>
@@ -840,23 +840,23 @@
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>Track_200</t>
+          <t>Track_Decel</t>
         </is>
       </c>
       <c r="C16" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="D16" t="n">
-        <v>0</v>
+        <v>1908</v>
       </c>
       <c r="E16" t="n">
-        <v>0</v>
+        <v>645</v>
       </c>
       <c r="F16" t="n">
-        <v>0</v>
+        <v>619</v>
       </c>
       <c r="G16" t="n">
-        <v>0</v>
+        <v>636</v>
       </c>
     </row>
     <row r="17">
@@ -867,23 +867,23 @@
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>Track_Accel</t>
+          <t>Track_UTurn_in</t>
         </is>
       </c>
       <c r="C17" t="n">
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="D17" t="n">
-        <v>1186</v>
+        <v>2478</v>
       </c>
       <c r="E17" t="n">
-        <v>645</v>
+        <v>599</v>
       </c>
       <c r="F17" t="n">
-        <v>541</v>
+        <v>417</v>
       </c>
       <c r="G17" t="n">
-        <v>593</v>
+        <v>495</v>
       </c>
     </row>
     <row r="18">
@@ -894,23 +894,23 @@
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>Track_Decel</t>
+          <t>Track_UTurn_out</t>
         </is>
       </c>
       <c r="C18" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="D18" t="n">
-        <v>1908</v>
+        <v>909</v>
       </c>
       <c r="E18" t="n">
-        <v>645</v>
+        <v>470</v>
       </c>
       <c r="F18" t="n">
-        <v>619</v>
+        <v>439</v>
       </c>
       <c r="G18" t="n">
-        <v>636</v>
+        <v>454</v>
       </c>
     </row>
     <row r="19">
@@ -921,23 +921,23 @@
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>Track_UTurn_in</t>
+          <t>Turn_F</t>
         </is>
       </c>
       <c r="C19" t="n">
         <v>5</v>
       </c>
       <c r="D19" t="n">
-        <v>2478</v>
+        <v>853</v>
       </c>
       <c r="E19" t="n">
-        <v>599</v>
+        <v>206</v>
       </c>
       <c r="F19" t="n">
-        <v>417</v>
+        <v>129</v>
       </c>
       <c r="G19" t="n">
-        <v>495</v>
+        <v>170</v>
       </c>
     </row>
     <row r="20">
@@ -948,23 +948,23 @@
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>Track_UTurn_out</t>
+          <t>Turn_L</t>
         </is>
       </c>
       <c r="C20" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="D20" t="n">
-        <v>909</v>
+        <v>412</v>
       </c>
       <c r="E20" t="n">
-        <v>470</v>
+        <v>412</v>
       </c>
       <c r="F20" t="n">
-        <v>439</v>
+        <v>412</v>
       </c>
       <c r="G20" t="n">
-        <v>454</v>
+        <v>412</v>
       </c>
     </row>
     <row r="21">
@@ -975,23 +975,23 @@
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>Turn_F</t>
+          <t>Turn_R</t>
         </is>
       </c>
       <c r="C21" t="n">
         <v>5</v>
       </c>
       <c r="D21" t="n">
-        <v>853</v>
+        <v>2339</v>
       </c>
       <c r="E21" t="n">
-        <v>206</v>
+        <v>514</v>
       </c>
       <c r="F21" t="n">
-        <v>129</v>
+        <v>411</v>
       </c>
       <c r="G21" t="n">
-        <v>170</v>
+        <v>467</v>
       </c>
     </row>
     <row r="22">
@@ -1002,23 +1002,23 @@
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>Turn_L</t>
+          <t>Turn_B</t>
         </is>
       </c>
       <c r="C22" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="D22" t="n">
-        <v>412</v>
+        <v>1992</v>
       </c>
       <c r="E22" t="n">
-        <v>412</v>
+        <v>1008</v>
       </c>
       <c r="F22" t="n">
-        <v>412</v>
+        <v>984</v>
       </c>
       <c r="G22" t="n">
-        <v>412</v>
+        <v>996</v>
       </c>
     </row>
     <row r="23">
@@ -1029,23 +1029,23 @@
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>Turn_R</t>
+          <t>Turn_T</t>
         </is>
       </c>
       <c r="C23" t="n">
-        <v>5</v>
+        <v>2</v>
       </c>
       <c r="D23" t="n">
-        <v>2339</v>
+        <v>1626</v>
       </c>
       <c r="E23" t="n">
-        <v>514</v>
+        <v>854</v>
       </c>
       <c r="F23" t="n">
-        <v>411</v>
+        <v>772</v>
       </c>
       <c r="G23" t="n">
-        <v>467</v>
+        <v>813</v>
       </c>
     </row>
     <row r="24">
@@ -1056,23 +1056,23 @@
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>Turn_B</t>
+          <t>Turn_LB</t>
         </is>
       </c>
       <c r="C24" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="D24" t="n">
-        <v>1992</v>
+        <v>488</v>
       </c>
       <c r="E24" t="n">
-        <v>1008</v>
+        <v>488</v>
       </c>
       <c r="F24" t="n">
-        <v>984</v>
+        <v>488</v>
       </c>
       <c r="G24" t="n">
-        <v>996</v>
+        <v>488</v>
       </c>
     </row>
     <row r="25">
@@ -1083,77 +1083,77 @@
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>Turn_T</t>
+          <t>Turn_RB</t>
         </is>
       </c>
       <c r="C25" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="D25" t="n">
-        <v>1626</v>
+        <v>412</v>
       </c>
       <c r="E25" t="n">
-        <v>854</v>
+        <v>412</v>
       </c>
       <c r="F25" t="n">
-        <v>772</v>
+        <v>412</v>
       </c>
       <c r="G25" t="n">
-        <v>813</v>
+        <v>412</v>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>Run_2</t>
+          <t>Run_3</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>Turn_LB</t>
+          <t>Track_150</t>
         </is>
       </c>
       <c r="C26" t="n">
         <v>1</v>
       </c>
       <c r="D26" t="n">
-        <v>488</v>
+        <v>568</v>
       </c>
       <c r="E26" t="n">
-        <v>488</v>
+        <v>568</v>
       </c>
       <c r="F26" t="n">
-        <v>488</v>
+        <v>568</v>
       </c>
       <c r="G26" t="n">
-        <v>488</v>
+        <v>568</v>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>Run_2</t>
+          <t>Run_3</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>Turn_RB</t>
+          <t>Track_200</t>
         </is>
       </c>
       <c r="C27" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="D27" t="n">
-        <v>412</v>
+        <v>1134</v>
       </c>
       <c r="E27" t="n">
-        <v>412</v>
+        <v>593</v>
       </c>
       <c r="F27" t="n">
-        <v>412</v>
+        <v>541</v>
       </c>
       <c r="G27" t="n">
-        <v>412</v>
+        <v>567</v>
       </c>
     </row>
     <row r="28">
@@ -1164,23 +1164,23 @@
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>Track_150</t>
+          <t>Track_Accel</t>
         </is>
       </c>
       <c r="C28" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="D28" t="n">
-        <v>568</v>
+        <v>1031</v>
       </c>
       <c r="E28" t="n">
-        <v>568</v>
+        <v>541</v>
       </c>
       <c r="F28" t="n">
-        <v>568</v>
+        <v>490</v>
       </c>
       <c r="G28" t="n">
-        <v>568</v>
+        <v>515</v>
       </c>
     </row>
     <row r="29">
@@ -1191,23 +1191,23 @@
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>Track_200</t>
+          <t>Track_Decel</t>
         </is>
       </c>
       <c r="C29" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="D29" t="n">
-        <v>1134</v>
+        <v>1807</v>
       </c>
       <c r="E29" t="n">
-        <v>593</v>
+        <v>619</v>
       </c>
       <c r="F29" t="n">
-        <v>541</v>
+        <v>594</v>
       </c>
       <c r="G29" t="n">
-        <v>567</v>
+        <v>602</v>
       </c>
     </row>
     <row r="30">
@@ -1218,23 +1218,23 @@
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>Track_Accel</t>
+          <t>Track_UTurn_in</t>
         </is>
       </c>
       <c r="C30" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="D30" t="n">
-        <v>1031</v>
+        <v>1462</v>
       </c>
       <c r="E30" t="n">
-        <v>541</v>
+        <v>547</v>
       </c>
       <c r="F30" t="n">
-        <v>490</v>
+        <v>394</v>
       </c>
       <c r="G30" t="n">
-        <v>515</v>
+        <v>487</v>
       </c>
     </row>
     <row r="31">
@@ -1245,23 +1245,23 @@
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>Track_Decel</t>
+          <t>Track_UTurn_out</t>
         </is>
       </c>
       <c r="C31" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="D31" t="n">
-        <v>1807</v>
+        <v>883</v>
       </c>
       <c r="E31" t="n">
-        <v>619</v>
+        <v>471</v>
       </c>
       <c r="F31" t="n">
-        <v>594</v>
+        <v>412</v>
       </c>
       <c r="G31" t="n">
-        <v>602</v>
+        <v>441</v>
       </c>
     </row>
     <row r="32">
@@ -1272,23 +1272,23 @@
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>Track_UTurn_in</t>
+          <t>Turn_F</t>
         </is>
       </c>
       <c r="C32" t="n">
-        <v>3</v>
+        <v>7</v>
       </c>
       <c r="D32" t="n">
-        <v>1462</v>
+        <v>1342</v>
       </c>
       <c r="E32" t="n">
-        <v>547</v>
+        <v>207</v>
       </c>
       <c r="F32" t="n">
-        <v>394</v>
+        <v>129</v>
       </c>
       <c r="G32" t="n">
-        <v>487</v>
+        <v>191</v>
       </c>
     </row>
     <row r="33">
@@ -1299,23 +1299,23 @@
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>Track_UTurn_out</t>
+          <t>Turn_L</t>
         </is>
       </c>
       <c r="C33" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="D33" t="n">
-        <v>883</v>
+        <v>462</v>
       </c>
       <c r="E33" t="n">
-        <v>471</v>
+        <v>462</v>
       </c>
       <c r="F33" t="n">
-        <v>412</v>
+        <v>462</v>
       </c>
       <c r="G33" t="n">
-        <v>441</v>
+        <v>462</v>
       </c>
     </row>
     <row r="34">
@@ -1326,23 +1326,23 @@
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>Turn_F</t>
+          <t>Turn_R</t>
         </is>
       </c>
       <c r="C34" t="n">
-        <v>7</v>
+        <v>3</v>
       </c>
       <c r="D34" t="n">
-        <v>1342</v>
+        <v>1514</v>
       </c>
       <c r="E34" t="n">
-        <v>207</v>
+        <v>539</v>
       </c>
       <c r="F34" t="n">
-        <v>129</v>
+        <v>487</v>
       </c>
       <c r="G34" t="n">
-        <v>191</v>
+        <v>504</v>
       </c>
     </row>
     <row r="35">
@@ -1353,77 +1353,77 @@
       </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t>Turn_L</t>
+          <t>Turn_T</t>
         </is>
       </c>
       <c r="C35" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="D35" t="n">
-        <v>462</v>
+        <v>1619</v>
       </c>
       <c r="E35" t="n">
-        <v>462</v>
+        <v>823</v>
       </c>
       <c r="F35" t="n">
-        <v>462</v>
+        <v>796</v>
       </c>
       <c r="G35" t="n">
-        <v>462</v>
+        <v>809</v>
       </c>
     </row>
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>Run_3</t>
+          <t>Run_4</t>
         </is>
       </c>
       <c r="B36" t="inlineStr">
         <is>
-          <t>Turn_R</t>
+          <t>Track_150</t>
         </is>
       </c>
       <c r="C36" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="D36" t="n">
-        <v>1514</v>
+        <v>541</v>
       </c>
       <c r="E36" t="n">
-        <v>539</v>
+        <v>541</v>
       </c>
       <c r="F36" t="n">
-        <v>487</v>
+        <v>541</v>
       </c>
       <c r="G36" t="n">
-        <v>504</v>
+        <v>541</v>
       </c>
     </row>
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>Run_3</t>
+          <t>Run_4</t>
         </is>
       </c>
       <c r="B37" t="inlineStr">
         <is>
-          <t>Turn_T</t>
+          <t>Track_200</t>
         </is>
       </c>
       <c r="C37" t="n">
         <v>2</v>
       </c>
       <c r="D37" t="n">
-        <v>1619</v>
+        <v>1135</v>
       </c>
       <c r="E37" t="n">
-        <v>823</v>
+        <v>594</v>
       </c>
       <c r="F37" t="n">
-        <v>796</v>
+        <v>541</v>
       </c>
       <c r="G37" t="n">
-        <v>809</v>
+        <v>567</v>
       </c>
     </row>
     <row r="38">
@@ -1434,23 +1434,23 @@
       </c>
       <c r="B38" t="inlineStr">
         <is>
-          <t>Track_150</t>
+          <t>Track_Accel</t>
         </is>
       </c>
       <c r="C38" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="D38" t="n">
-        <v>541</v>
+        <v>955</v>
       </c>
       <c r="E38" t="n">
-        <v>541</v>
+        <v>491</v>
       </c>
       <c r="F38" t="n">
-        <v>541</v>
+        <v>464</v>
       </c>
       <c r="G38" t="n">
-        <v>541</v>
+        <v>477</v>
       </c>
     </row>
     <row r="39">
@@ -1461,23 +1461,23 @@
       </c>
       <c r="B39" t="inlineStr">
         <is>
-          <t>Track_200</t>
+          <t>Track_Decel</t>
         </is>
       </c>
       <c r="C39" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="D39" t="n">
-        <v>1135</v>
+        <v>1831</v>
       </c>
       <c r="E39" t="n">
-        <v>594</v>
+        <v>645</v>
       </c>
       <c r="F39" t="n">
-        <v>541</v>
+        <v>593</v>
       </c>
       <c r="G39" t="n">
-        <v>567</v>
+        <v>610</v>
       </c>
     </row>
     <row r="40">
@@ -1488,23 +1488,23 @@
       </c>
       <c r="B40" t="inlineStr">
         <is>
-          <t>Track_Accel</t>
+          <t>Track_UTurn_in</t>
         </is>
       </c>
       <c r="C40" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="D40" t="n">
-        <v>955</v>
+        <v>1460</v>
       </c>
       <c r="E40" t="n">
-        <v>491</v>
+        <v>547</v>
       </c>
       <c r="F40" t="n">
-        <v>464</v>
+        <v>392</v>
       </c>
       <c r="G40" t="n">
-        <v>477</v>
+        <v>486</v>
       </c>
     </row>
     <row r="41">
@@ -1515,23 +1515,23 @@
       </c>
       <c r="B41" t="inlineStr">
         <is>
-          <t>Track_Decel</t>
+          <t>Track_UTurn_out</t>
         </is>
       </c>
       <c r="C41" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="D41" t="n">
-        <v>1831</v>
+        <v>891</v>
       </c>
       <c r="E41" t="n">
-        <v>645</v>
+        <v>446</v>
       </c>
       <c r="F41" t="n">
-        <v>593</v>
+        <v>445</v>
       </c>
       <c r="G41" t="n">
-        <v>610</v>
+        <v>445</v>
       </c>
     </row>
     <row r="42">
@@ -1542,23 +1542,23 @@
       </c>
       <c r="B42" t="inlineStr">
         <is>
-          <t>Track_UTurn_in</t>
+          <t>Turn_F</t>
         </is>
       </c>
       <c r="C42" t="n">
-        <v>3</v>
+        <v>7</v>
       </c>
       <c r="D42" t="n">
-        <v>1460</v>
+        <v>1366</v>
       </c>
       <c r="E42" t="n">
-        <v>547</v>
+        <v>207</v>
       </c>
       <c r="F42" t="n">
-        <v>392</v>
+        <v>129</v>
       </c>
       <c r="G42" t="n">
-        <v>486</v>
+        <v>195</v>
       </c>
     </row>
     <row r="43">
@@ -1569,23 +1569,23 @@
       </c>
       <c r="B43" t="inlineStr">
         <is>
-          <t>Track_UTurn_out</t>
+          <t>Turn_L</t>
         </is>
       </c>
       <c r="C43" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="D43" t="n">
-        <v>891</v>
+        <v>565</v>
       </c>
       <c r="E43" t="n">
-        <v>446</v>
+        <v>565</v>
       </c>
       <c r="F43" t="n">
-        <v>445</v>
+        <v>565</v>
       </c>
       <c r="G43" t="n">
-        <v>445</v>
+        <v>565</v>
       </c>
     </row>
     <row r="44">
@@ -1596,23 +1596,23 @@
       </c>
       <c r="B44" t="inlineStr">
         <is>
-          <t>Turn_F</t>
+          <t>Turn_R</t>
         </is>
       </c>
       <c r="C44" t="n">
-        <v>7</v>
+        <v>3</v>
       </c>
       <c r="D44" t="n">
-        <v>1366</v>
+        <v>1646</v>
       </c>
       <c r="E44" t="n">
-        <v>207</v>
+        <v>566</v>
       </c>
       <c r="F44" t="n">
-        <v>129</v>
+        <v>540</v>
       </c>
       <c r="G44" t="n">
-        <v>195</v>
+        <v>548</v>
       </c>
     </row>
     <row r="45">
@@ -1623,77 +1623,77 @@
       </c>
       <c r="B45" t="inlineStr">
         <is>
-          <t>Turn_L</t>
+          <t>Turn_T</t>
         </is>
       </c>
       <c r="C45" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="D45" t="n">
-        <v>565</v>
+        <v>1517</v>
       </c>
       <c r="E45" t="n">
-        <v>565</v>
+        <v>797</v>
       </c>
       <c r="F45" t="n">
-        <v>565</v>
+        <v>720</v>
       </c>
       <c r="G45" t="n">
-        <v>565</v>
+        <v>758</v>
       </c>
     </row>
     <row r="46">
       <c r="A46" t="inlineStr">
         <is>
-          <t>Run_4</t>
+          <t>Run_5</t>
         </is>
       </c>
       <c r="B46" t="inlineStr">
         <is>
-          <t>Turn_R</t>
+          <t>Track_150</t>
         </is>
       </c>
       <c r="C46" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="D46" t="n">
-        <v>1646</v>
+        <v>515</v>
       </c>
       <c r="E46" t="n">
-        <v>566</v>
+        <v>515</v>
       </c>
       <c r="F46" t="n">
-        <v>540</v>
+        <v>515</v>
       </c>
       <c r="G46" t="n">
-        <v>548</v>
+        <v>515</v>
       </c>
     </row>
     <row r="47">
       <c r="A47" t="inlineStr">
         <is>
-          <t>Run_4</t>
+          <t>Run_5</t>
         </is>
       </c>
       <c r="B47" t="inlineStr">
         <is>
-          <t>Turn_T</t>
+          <t>Track_200</t>
         </is>
       </c>
       <c r="C47" t="n">
         <v>2</v>
       </c>
       <c r="D47" t="n">
-        <v>1517</v>
+        <v>1210</v>
       </c>
       <c r="E47" t="n">
-        <v>797</v>
+        <v>644</v>
       </c>
       <c r="F47" t="n">
-        <v>720</v>
+        <v>566</v>
       </c>
       <c r="G47" t="n">
-        <v>758</v>
+        <v>605</v>
       </c>
     </row>
     <row r="48">
@@ -1704,17 +1704,17 @@
       </c>
       <c r="B48" t="inlineStr">
         <is>
-          <t>Track_150</t>
+          <t>Track_Accel</t>
         </is>
       </c>
       <c r="C48" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="D48" t="n">
-        <v>515</v>
+        <v>1031</v>
       </c>
       <c r="E48" t="n">
-        <v>515</v>
+        <v>516</v>
       </c>
       <c r="F48" t="n">
         <v>515</v>
@@ -1731,23 +1731,23 @@
       </c>
       <c r="B49" t="inlineStr">
         <is>
-          <t>Track_200</t>
+          <t>Track_Decel</t>
         </is>
       </c>
       <c r="C49" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="D49" t="n">
-        <v>1210</v>
+        <v>1806</v>
       </c>
       <c r="E49" t="n">
-        <v>644</v>
+        <v>619</v>
       </c>
       <c r="F49" t="n">
-        <v>566</v>
+        <v>593</v>
       </c>
       <c r="G49" t="n">
-        <v>605</v>
+        <v>602</v>
       </c>
     </row>
     <row r="50">
@@ -1758,23 +1758,23 @@
       </c>
       <c r="B50" t="inlineStr">
         <is>
-          <t>Track_Accel</t>
+          <t>Track_UTurn_in</t>
         </is>
       </c>
       <c r="C50" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="D50" t="n">
-        <v>1031</v>
+        <v>1487</v>
       </c>
       <c r="E50" t="n">
-        <v>516</v>
+        <v>573</v>
       </c>
       <c r="F50" t="n">
-        <v>515</v>
+        <v>393</v>
       </c>
       <c r="G50" t="n">
-        <v>515</v>
+        <v>495</v>
       </c>
     </row>
     <row r="51">
@@ -1785,23 +1785,23 @@
       </c>
       <c r="B51" t="inlineStr">
         <is>
-          <t>Track_Decel</t>
+          <t>Track_UTurn_out</t>
         </is>
       </c>
       <c r="C51" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="D51" t="n">
-        <v>1806</v>
+        <v>890</v>
       </c>
       <c r="E51" t="n">
-        <v>619</v>
+        <v>445</v>
       </c>
       <c r="F51" t="n">
-        <v>593</v>
+        <v>445</v>
       </c>
       <c r="G51" t="n">
-        <v>602</v>
+        <v>445</v>
       </c>
     </row>
     <row r="52">
@@ -1812,23 +1812,23 @@
       </c>
       <c r="B52" t="inlineStr">
         <is>
-          <t>Track_UTurn_in</t>
+          <t>Turn_F</t>
         </is>
       </c>
       <c r="C52" t="n">
-        <v>3</v>
+        <v>7</v>
       </c>
       <c r="D52" t="n">
-        <v>1487</v>
+        <v>1266</v>
       </c>
       <c r="E52" t="n">
-        <v>573</v>
+        <v>233</v>
       </c>
       <c r="F52" t="n">
-        <v>393</v>
+        <v>129</v>
       </c>
       <c r="G52" t="n">
-        <v>495</v>
+        <v>180</v>
       </c>
     </row>
     <row r="53">
@@ -1839,23 +1839,23 @@
       </c>
       <c r="B53" t="inlineStr">
         <is>
-          <t>Track_UTurn_out</t>
+          <t>Turn_L</t>
         </is>
       </c>
       <c r="C53" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="D53" t="n">
-        <v>890</v>
+        <v>540</v>
       </c>
       <c r="E53" t="n">
-        <v>445</v>
+        <v>540</v>
       </c>
       <c r="F53" t="n">
-        <v>445</v>
+        <v>540</v>
       </c>
       <c r="G53" t="n">
-        <v>445</v>
+        <v>540</v>
       </c>
     </row>
     <row r="54">
@@ -1866,23 +1866,23 @@
       </c>
       <c r="B54" t="inlineStr">
         <is>
-          <t>Turn_F</t>
+          <t>Turn_R</t>
         </is>
       </c>
       <c r="C54" t="n">
-        <v>7</v>
+        <v>3</v>
       </c>
       <c r="D54" t="n">
-        <v>1266</v>
+        <v>1567</v>
       </c>
       <c r="E54" t="n">
-        <v>233</v>
+        <v>540</v>
       </c>
       <c r="F54" t="n">
-        <v>129</v>
+        <v>488</v>
       </c>
       <c r="G54" t="n">
-        <v>180</v>
+        <v>522</v>
       </c>
     </row>
     <row r="55">
@@ -1893,725 +1893,2750 @@
       </c>
       <c r="B55" t="inlineStr">
         <is>
-          <t>Turn_L</t>
+          <t>Turn_T</t>
         </is>
       </c>
       <c r="C55" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="D55" t="n">
-        <v>540</v>
+        <v>1567</v>
       </c>
       <c r="E55" t="n">
-        <v>540</v>
+        <v>822</v>
       </c>
       <c r="F55" t="n">
-        <v>540</v>
+        <v>745</v>
       </c>
       <c r="G55" t="n">
-        <v>540</v>
+        <v>783</v>
       </c>
     </row>
     <row r="56">
       <c r="A56" t="inlineStr">
         <is>
-          <t>Run_5</t>
+          <t>Run_6</t>
         </is>
       </c>
       <c r="B56" t="inlineStr">
         <is>
-          <t>Turn_R</t>
+          <t>Track_150</t>
         </is>
       </c>
       <c r="C56" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="D56" t="n">
-        <v>1567</v>
+        <v>2349</v>
       </c>
       <c r="E56" t="n">
-        <v>540</v>
+        <v>645</v>
       </c>
       <c r="F56" t="n">
-        <v>488</v>
+        <v>542</v>
       </c>
       <c r="G56" t="n">
-        <v>522</v>
+        <v>587</v>
       </c>
     </row>
     <row r="57">
       <c r="A57" t="inlineStr">
         <is>
-          <t>Run_5</t>
+          <t>Run_6</t>
         </is>
       </c>
       <c r="B57" t="inlineStr">
         <is>
-          <t>Turn_T</t>
+          <t>Track_200</t>
         </is>
       </c>
       <c r="C57" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="D57" t="n">
-        <v>1567</v>
+        <v>592</v>
       </c>
       <c r="E57" t="n">
-        <v>822</v>
+        <v>592</v>
       </c>
       <c r="F57" t="n">
-        <v>745</v>
+        <v>592</v>
       </c>
       <c r="G57" t="n">
-        <v>783</v>
+        <v>592</v>
       </c>
     </row>
     <row r="58">
       <c r="A58" t="inlineStr">
         <is>
-          <t>Run_9</t>
+          <t>Run_6</t>
         </is>
       </c>
       <c r="B58" t="inlineStr">
         <is>
-          <t>Track_150</t>
+          <t>Track_Accel</t>
         </is>
       </c>
       <c r="C58" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="D58" t="n">
-        <v>2349</v>
+        <v>1059</v>
       </c>
       <c r="E58" t="n">
-        <v>645</v>
+        <v>543</v>
       </c>
       <c r="F58" t="n">
-        <v>542</v>
+        <v>516</v>
       </c>
       <c r="G58" t="n">
-        <v>587</v>
+        <v>529</v>
       </c>
     </row>
     <row r="59">
       <c r="A59" t="inlineStr">
         <is>
-          <t>Run_9</t>
+          <t>Run_6</t>
         </is>
       </c>
       <c r="B59" t="inlineStr">
         <is>
-          <t>Track_200</t>
+          <t>Track_Decel</t>
         </is>
       </c>
       <c r="C59" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="D59" t="n">
-        <v>592</v>
+        <v>1803</v>
       </c>
       <c r="E59" t="n">
-        <v>592</v>
+        <v>618</v>
       </c>
       <c r="F59" t="n">
         <v>592</v>
       </c>
       <c r="G59" t="n">
-        <v>592</v>
+        <v>601</v>
       </c>
     </row>
     <row r="60">
       <c r="A60" t="inlineStr">
         <is>
-          <t>Run_9</t>
+          <t>Run_6</t>
         </is>
       </c>
       <c r="B60" t="inlineStr">
         <is>
-          <t>Track_Accel</t>
+          <t>Track_UTurn_in</t>
         </is>
       </c>
       <c r="C60" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="D60" t="n">
-        <v>1059</v>
+        <v>1957</v>
       </c>
       <c r="E60" t="n">
-        <v>543</v>
+        <v>574</v>
       </c>
       <c r="F60" t="n">
-        <v>516</v>
+        <v>393</v>
       </c>
       <c r="G60" t="n">
-        <v>529</v>
+        <v>489</v>
       </c>
     </row>
     <row r="61">
       <c r="A61" t="inlineStr">
         <is>
-          <t>Run_9</t>
+          <t>Run_6</t>
         </is>
       </c>
       <c r="B61" t="inlineStr">
         <is>
-          <t>Track_Decel</t>
+          <t>Track_UTurn_out</t>
         </is>
       </c>
       <c r="C61" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="D61" t="n">
-        <v>1803</v>
+        <v>884</v>
       </c>
       <c r="E61" t="n">
-        <v>618</v>
+        <v>445</v>
       </c>
       <c r="F61" t="n">
-        <v>592</v>
+        <v>439</v>
       </c>
       <c r="G61" t="n">
-        <v>601</v>
+        <v>442</v>
       </c>
     </row>
     <row r="62">
       <c r="A62" t="inlineStr">
         <is>
-          <t>Run_9</t>
+          <t>Run_6</t>
         </is>
       </c>
       <c r="B62" t="inlineStr">
         <is>
-          <t>Track_UTurn_in</t>
+          <t>Turn_F</t>
         </is>
       </c>
       <c r="C62" t="n">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="D62" t="n">
-        <v>1957</v>
+        <v>1161</v>
       </c>
       <c r="E62" t="n">
-        <v>574</v>
+        <v>207</v>
       </c>
       <c r="F62" t="n">
-        <v>393</v>
+        <v>155</v>
       </c>
       <c r="G62" t="n">
-        <v>489</v>
+        <v>193</v>
       </c>
     </row>
     <row r="63">
       <c r="A63" t="inlineStr">
         <is>
-          <t>Run_9</t>
+          <t>Run_6</t>
         </is>
       </c>
       <c r="B63" t="inlineStr">
         <is>
-          <t>Track_UTurn_out</t>
+          <t>Turn_L</t>
         </is>
       </c>
       <c r="C63" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="D63" t="n">
-        <v>884</v>
+        <v>1387</v>
       </c>
       <c r="E63" t="n">
-        <v>445</v>
+        <v>488</v>
       </c>
       <c r="F63" t="n">
-        <v>439</v>
+        <v>411</v>
       </c>
       <c r="G63" t="n">
-        <v>442</v>
+        <v>462</v>
       </c>
     </row>
     <row r="64">
       <c r="A64" t="inlineStr">
         <is>
-          <t>Run_9</t>
+          <t>Run_6</t>
         </is>
       </c>
       <c r="B64" t="inlineStr">
         <is>
-          <t>Turn_F</t>
+          <t>Turn_R</t>
         </is>
       </c>
       <c r="C64" t="n">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="D64" t="n">
-        <v>1161</v>
+        <v>2003</v>
       </c>
       <c r="E64" t="n">
-        <v>207</v>
+        <v>565</v>
       </c>
       <c r="F64" t="n">
-        <v>155</v>
+        <v>462</v>
       </c>
       <c r="G64" t="n">
-        <v>193</v>
+        <v>500</v>
       </c>
     </row>
     <row r="65">
       <c r="A65" t="inlineStr">
         <is>
-          <t>Run_9</t>
+          <t>Run_6</t>
         </is>
       </c>
       <c r="B65" t="inlineStr">
         <is>
-          <t>Turn_L</t>
+          <t>Turn_B</t>
         </is>
       </c>
       <c r="C65" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="D65" t="n">
-        <v>1387</v>
+        <v>1008</v>
       </c>
       <c r="E65" t="n">
-        <v>488</v>
+        <v>1008</v>
       </c>
       <c r="F65" t="n">
-        <v>411</v>
+        <v>1008</v>
       </c>
       <c r="G65" t="n">
-        <v>462</v>
+        <v>1008</v>
       </c>
     </row>
     <row r="66">
       <c r="A66" t="inlineStr">
         <is>
-          <t>Run_9</t>
+          <t>Run_6</t>
         </is>
       </c>
       <c r="B66" t="inlineStr">
         <is>
-          <t>Turn_R</t>
+          <t>Turn_T</t>
         </is>
       </c>
       <c r="C66" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="D66" t="n">
-        <v>2003</v>
+        <v>1523</v>
       </c>
       <c r="E66" t="n">
-        <v>565</v>
+        <v>803</v>
       </c>
       <c r="F66" t="n">
-        <v>462</v>
+        <v>720</v>
       </c>
       <c r="G66" t="n">
-        <v>500</v>
+        <v>761</v>
       </c>
     </row>
     <row r="67">
       <c r="A67" t="inlineStr">
         <is>
-          <t>Run_9</t>
+          <t>Run_6</t>
         </is>
       </c>
       <c r="B67" t="inlineStr">
         <is>
-          <t>Turn_B</t>
+          <t>Turn_LB</t>
         </is>
       </c>
       <c r="C67" t="n">
         <v>1</v>
       </c>
       <c r="D67" t="n">
-        <v>1008</v>
+        <v>463</v>
       </c>
       <c r="E67" t="n">
-        <v>1008</v>
+        <v>463</v>
       </c>
       <c r="F67" t="n">
-        <v>1008</v>
+        <v>463</v>
       </c>
       <c r="G67" t="n">
-        <v>1008</v>
+        <v>463</v>
       </c>
     </row>
     <row r="68">
       <c r="A68" t="inlineStr">
         <is>
-          <t>Run_9</t>
+          <t>Run_7</t>
         </is>
       </c>
       <c r="B68" t="inlineStr">
         <is>
-          <t>Turn_T</t>
+          <t>Track_150</t>
         </is>
       </c>
       <c r="C68" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="D68" t="n">
-        <v>1523</v>
+        <v>2349</v>
       </c>
       <c r="E68" t="n">
-        <v>803</v>
+        <v>646</v>
       </c>
       <c r="F68" t="n">
-        <v>720</v>
+        <v>542</v>
       </c>
       <c r="G68" t="n">
-        <v>761</v>
+        <v>587</v>
       </c>
     </row>
     <row r="69">
       <c r="A69" t="inlineStr">
         <is>
-          <t>Run_9</t>
+          <t>Run_7</t>
         </is>
       </c>
       <c r="B69" t="inlineStr">
         <is>
-          <t>Turn_LB</t>
+          <t>Track_200</t>
         </is>
       </c>
       <c r="C69" t="n">
         <v>1</v>
       </c>
       <c r="D69" t="n">
-        <v>463</v>
+        <v>620</v>
       </c>
       <c r="E69" t="n">
-        <v>463</v>
+        <v>620</v>
       </c>
       <c r="F69" t="n">
-        <v>463</v>
+        <v>620</v>
       </c>
       <c r="G69" t="n">
-        <v>463</v>
+        <v>620</v>
       </c>
     </row>
     <row r="70">
       <c r="A70" t="inlineStr">
         <is>
-          <t>Run_10</t>
+          <t>Run_7</t>
         </is>
       </c>
       <c r="B70" t="inlineStr">
         <is>
-          <t>Track_150</t>
+          <t>Track_Accel</t>
         </is>
       </c>
       <c r="C70" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="D70" t="n">
-        <v>2349</v>
+        <v>1057</v>
       </c>
       <c r="E70" t="n">
-        <v>646</v>
+        <v>567</v>
       </c>
       <c r="F70" t="n">
-        <v>542</v>
+        <v>490</v>
       </c>
       <c r="G70" t="n">
-        <v>587</v>
+        <v>528</v>
       </c>
     </row>
     <row r="71">
       <c r="A71" t="inlineStr">
         <is>
-          <t>Run_10</t>
+          <t>Run_7</t>
         </is>
       </c>
       <c r="B71" t="inlineStr">
         <is>
-          <t>Track_200</t>
+          <t>Track_Decel</t>
         </is>
       </c>
       <c r="C71" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="D71" t="n">
-        <v>620</v>
+        <v>1831</v>
       </c>
       <c r="E71" t="n">
-        <v>620</v>
+        <v>619</v>
       </c>
       <c r="F71" t="n">
-        <v>620</v>
+        <v>593</v>
       </c>
       <c r="G71" t="n">
-        <v>620</v>
+        <v>610</v>
       </c>
     </row>
     <row r="72">
       <c r="A72" t="inlineStr">
         <is>
-          <t>Run_10</t>
+          <t>Run_7</t>
         </is>
       </c>
       <c r="B72" t="inlineStr">
         <is>
-          <t>Track_Accel</t>
+          <t>Track_UTurn_in</t>
         </is>
       </c>
       <c r="C72" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="D72" t="n">
-        <v>1057</v>
+        <v>1829</v>
       </c>
       <c r="E72" t="n">
-        <v>567</v>
+        <v>522</v>
       </c>
       <c r="F72" t="n">
-        <v>490</v>
+        <v>393</v>
       </c>
       <c r="G72" t="n">
-        <v>528</v>
+        <v>457</v>
       </c>
     </row>
     <row r="73">
       <c r="A73" t="inlineStr">
         <is>
-          <t>Run_10</t>
+          <t>Run_7</t>
         </is>
       </c>
       <c r="B73" t="inlineStr">
         <is>
-          <t>Track_Decel</t>
+          <t>Track_UTurn_out</t>
         </is>
       </c>
       <c r="C73" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="D73" t="n">
-        <v>1831</v>
+        <v>885</v>
       </c>
       <c r="E73" t="n">
-        <v>619</v>
+        <v>446</v>
       </c>
       <c r="F73" t="n">
-        <v>593</v>
+        <v>439</v>
       </c>
       <c r="G73" t="n">
-        <v>610</v>
+        <v>442</v>
       </c>
     </row>
     <row r="74">
       <c r="A74" t="inlineStr">
         <is>
-          <t>Run_10</t>
+          <t>Run_7</t>
         </is>
       </c>
       <c r="B74" t="inlineStr">
         <is>
-          <t>Track_UTurn_in</t>
+          <t>Turn_F</t>
         </is>
       </c>
       <c r="C74" t="n">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="D74" t="n">
-        <v>1829</v>
+        <v>1084</v>
       </c>
       <c r="E74" t="n">
-        <v>522</v>
+        <v>207</v>
       </c>
       <c r="F74" t="n">
-        <v>393</v>
+        <v>129</v>
       </c>
       <c r="G74" t="n">
-        <v>457</v>
+        <v>180</v>
       </c>
     </row>
     <row r="75">
       <c r="A75" t="inlineStr">
         <is>
-          <t>Run_10</t>
+          <t>Run_7</t>
         </is>
       </c>
       <c r="B75" t="inlineStr">
         <is>
-          <t>Track_UTurn_out</t>
+          <t>Turn_L</t>
         </is>
       </c>
       <c r="C75" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="D75" t="n">
-        <v>885</v>
+        <v>1464</v>
       </c>
       <c r="E75" t="n">
-        <v>446</v>
+        <v>514</v>
       </c>
       <c r="F75" t="n">
-        <v>439</v>
+        <v>437</v>
       </c>
       <c r="G75" t="n">
-        <v>442</v>
+        <v>488</v>
       </c>
     </row>
     <row r="76">
       <c r="A76" t="inlineStr">
         <is>
-          <t>Run_10</t>
+          <t>Run_7</t>
         </is>
       </c>
       <c r="B76" t="inlineStr">
         <is>
-          <t>Turn_F</t>
+          <t>Turn_R</t>
         </is>
       </c>
       <c r="C76" t="n">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="D76" t="n">
-        <v>1084</v>
+        <v>1875</v>
       </c>
       <c r="E76" t="n">
-        <v>207</v>
+        <v>488</v>
       </c>
       <c r="F76" t="n">
-        <v>129</v>
+        <v>436</v>
       </c>
       <c r="G76" t="n">
-        <v>180</v>
+        <v>468</v>
       </c>
     </row>
     <row r="77">
       <c r="A77" t="inlineStr">
         <is>
-          <t>Run_10</t>
+          <t>Run_7</t>
         </is>
       </c>
       <c r="B77" t="inlineStr">
         <is>
-          <t>Turn_L</t>
+          <t>Turn_B</t>
         </is>
       </c>
       <c r="C77" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="D77" t="n">
-        <v>1464</v>
+        <v>1086</v>
       </c>
       <c r="E77" t="n">
-        <v>514</v>
+        <v>1086</v>
       </c>
       <c r="F77" t="n">
-        <v>437</v>
+        <v>1086</v>
       </c>
       <c r="G77" t="n">
-        <v>488</v>
+        <v>1086</v>
       </c>
     </row>
     <row r="78">
       <c r="A78" t="inlineStr">
         <is>
-          <t>Run_10</t>
+          <t>Run_7</t>
         </is>
       </c>
       <c r="B78" t="inlineStr">
         <is>
-          <t>Turn_R</t>
+          <t>Turn_T</t>
         </is>
       </c>
       <c r="C78" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="D78" t="n">
-        <v>1875</v>
+        <v>1524</v>
       </c>
       <c r="E78" t="n">
-        <v>488</v>
+        <v>798</v>
       </c>
       <c r="F78" t="n">
-        <v>436</v>
+        <v>726</v>
       </c>
       <c r="G78" t="n">
-        <v>468</v>
+        <v>762</v>
       </c>
     </row>
     <row r="79">
       <c r="A79" t="inlineStr">
         <is>
-          <t>Run_10</t>
+          <t>Run_7</t>
         </is>
       </c>
       <c r="B79" t="inlineStr">
         <is>
-          <t>Turn_B</t>
+          <t>Turn_LB</t>
         </is>
       </c>
       <c r="C79" t="n">
         <v>1</v>
       </c>
       <c r="D79" t="n">
-        <v>1086</v>
+        <v>462</v>
       </c>
       <c r="E79" t="n">
-        <v>1086</v>
+        <v>462</v>
       </c>
       <c r="F79" t="n">
-        <v>1086</v>
+        <v>462</v>
       </c>
       <c r="G79" t="n">
-        <v>1086</v>
+        <v>462</v>
       </c>
     </row>
     <row r="80">
       <c r="A80" t="inlineStr">
         <is>
-          <t>Run_10</t>
+          <t>Run_8</t>
         </is>
       </c>
       <c r="B80" t="inlineStr">
         <is>
-          <t>Turn_T</t>
+          <t>Track_150</t>
         </is>
       </c>
       <c r="C80" t="n">
-        <v>2</v>
+        <v>6</v>
       </c>
       <c r="D80" t="n">
-        <v>1524</v>
+        <v>3507</v>
       </c>
       <c r="E80" t="n">
-        <v>798</v>
+        <v>645</v>
       </c>
       <c r="F80" t="n">
-        <v>726</v>
+        <v>542</v>
       </c>
       <c r="G80" t="n">
-        <v>762</v>
+        <v>584</v>
       </c>
     </row>
     <row r="81">
       <c r="A81" t="inlineStr">
         <is>
+          <t>Run_8</t>
+        </is>
+      </c>
+      <c r="B81" t="inlineStr">
+        <is>
+          <t>Track_200</t>
+        </is>
+      </c>
+      <c r="C81" t="n">
+        <v>2</v>
+      </c>
+      <c r="D81" t="n">
+        <v>1134</v>
+      </c>
+      <c r="E81" t="n">
+        <v>592</v>
+      </c>
+      <c r="F81" t="n">
+        <v>542</v>
+      </c>
+      <c r="G81" t="n">
+        <v>567</v>
+      </c>
+    </row>
+    <row r="82">
+      <c r="A82" t="inlineStr">
+        <is>
+          <t>Run_8</t>
+        </is>
+      </c>
+      <c r="B82" t="inlineStr">
+        <is>
+          <t>Track_Accel</t>
+        </is>
+      </c>
+      <c r="C82" t="n">
+        <v>2</v>
+      </c>
+      <c r="D82" t="n">
+        <v>1032</v>
+      </c>
+      <c r="E82" t="n">
+        <v>542</v>
+      </c>
+      <c r="F82" t="n">
+        <v>490</v>
+      </c>
+      <c r="G82" t="n">
+        <v>516</v>
+      </c>
+    </row>
+    <row r="83">
+      <c r="A83" t="inlineStr">
+        <is>
+          <t>Run_8</t>
+        </is>
+      </c>
+      <c r="B83" t="inlineStr">
+        <is>
+          <t>Track_Decel</t>
+        </is>
+      </c>
+      <c r="C83" t="n">
+        <v>3</v>
+      </c>
+      <c r="D83" t="n">
+        <v>1831</v>
+      </c>
+      <c r="E83" t="n">
+        <v>645</v>
+      </c>
+      <c r="F83" t="n">
+        <v>593</v>
+      </c>
+      <c r="G83" t="n">
+        <v>610</v>
+      </c>
+    </row>
+    <row r="84">
+      <c r="A84" t="inlineStr">
+        <is>
+          <t>Run_8</t>
+        </is>
+      </c>
+      <c r="B84" t="inlineStr">
+        <is>
+          <t>Track_UTurn_in</t>
+        </is>
+      </c>
+      <c r="C84" t="n">
+        <v>5</v>
+      </c>
+      <c r="D84" t="n">
+        <v>2324</v>
+      </c>
+      <c r="E84" t="n">
+        <v>548</v>
+      </c>
+      <c r="F84" t="n">
+        <v>392</v>
+      </c>
+      <c r="G84" t="n">
+        <v>464</v>
+      </c>
+    </row>
+    <row r="85">
+      <c r="A85" t="inlineStr">
+        <is>
+          <t>Run_8</t>
+        </is>
+      </c>
+      <c r="B85" t="inlineStr">
+        <is>
+          <t>Track_UTurn_out</t>
+        </is>
+      </c>
+      <c r="C85" t="n">
+        <v>2</v>
+      </c>
+      <c r="D85" t="n">
+        <v>850</v>
+      </c>
+      <c r="E85" t="n">
+        <v>438</v>
+      </c>
+      <c r="F85" t="n">
+        <v>412</v>
+      </c>
+      <c r="G85" t="n">
+        <v>425</v>
+      </c>
+    </row>
+    <row r="86">
+      <c r="A86" t="inlineStr">
+        <is>
+          <t>Run_8</t>
+        </is>
+      </c>
+      <c r="B86" t="inlineStr">
+        <is>
+          <t>Turn_F</t>
+        </is>
+      </c>
+      <c r="C86" t="n">
+        <v>7</v>
+      </c>
+      <c r="D86" t="n">
+        <v>1343</v>
+      </c>
+      <c r="E86" t="n">
+        <v>233</v>
+      </c>
+      <c r="F86" t="n">
+        <v>129</v>
+      </c>
+      <c r="G86" t="n">
+        <v>191</v>
+      </c>
+    </row>
+    <row r="87">
+      <c r="A87" t="inlineStr">
+        <is>
+          <t>Run_8</t>
+        </is>
+      </c>
+      <c r="B87" t="inlineStr">
+        <is>
+          <t>Turn_L</t>
+        </is>
+      </c>
+      <c r="C87" t="n">
+        <v>3</v>
+      </c>
+      <c r="D87" t="n">
+        <v>1465</v>
+      </c>
+      <c r="E87" t="n">
+        <v>565</v>
+      </c>
+      <c r="F87" t="n">
+        <v>411</v>
+      </c>
+      <c r="G87" t="n">
+        <v>488</v>
+      </c>
+    </row>
+    <row r="88">
+      <c r="A88" t="inlineStr">
+        <is>
+          <t>Run_8</t>
+        </is>
+      </c>
+      <c r="B88" t="inlineStr">
+        <is>
+          <t>Turn_R</t>
+        </is>
+      </c>
+      <c r="C88" t="n">
+        <v>6</v>
+      </c>
+      <c r="D88" t="n">
+        <v>2878</v>
+      </c>
+      <c r="E88" t="n">
+        <v>539</v>
+      </c>
+      <c r="F88" t="n">
+        <v>412</v>
+      </c>
+      <c r="G88" t="n">
+        <v>479</v>
+      </c>
+    </row>
+    <row r="89">
+      <c r="A89" t="inlineStr">
+        <is>
+          <t>Run_8</t>
+        </is>
+      </c>
+      <c r="B89" t="inlineStr">
+        <is>
+          <t>Turn_B</t>
+        </is>
+      </c>
+      <c r="C89" t="n">
+        <v>2</v>
+      </c>
+      <c r="D89" t="n">
+        <v>2017</v>
+      </c>
+      <c r="E89" t="n">
+        <v>1009</v>
+      </c>
+      <c r="F89" t="n">
+        <v>1008</v>
+      </c>
+      <c r="G89" t="n">
+        <v>1008</v>
+      </c>
+    </row>
+    <row r="90">
+      <c r="A90" t="inlineStr">
+        <is>
+          <t>Run_8</t>
+        </is>
+      </c>
+      <c r="B90" t="inlineStr">
+        <is>
+          <t>Turn_T</t>
+        </is>
+      </c>
+      <c r="C90" t="n">
+        <v>2</v>
+      </c>
+      <c r="D90" t="n">
+        <v>1555</v>
+      </c>
+      <c r="E90" t="n">
+        <v>803</v>
+      </c>
+      <c r="F90" t="n">
+        <v>752</v>
+      </c>
+      <c r="G90" t="n">
+        <v>777</v>
+      </c>
+    </row>
+    <row r="91">
+      <c r="A91" t="inlineStr">
+        <is>
+          <t>Run_8</t>
+        </is>
+      </c>
+      <c r="B91" t="inlineStr">
+        <is>
+          <t>Turn_LB</t>
+        </is>
+      </c>
+      <c r="C91" t="n">
+        <v>1</v>
+      </c>
+      <c r="D91" t="n">
+        <v>412</v>
+      </c>
+      <c r="E91" t="n">
+        <v>412</v>
+      </c>
+      <c r="F91" t="n">
+        <v>412</v>
+      </c>
+      <c r="G91" t="n">
+        <v>412</v>
+      </c>
+    </row>
+    <row r="92">
+      <c r="A92" t="inlineStr">
+        <is>
+          <t>Run_8</t>
+        </is>
+      </c>
+      <c r="B92" t="inlineStr">
+        <is>
+          <t>Turn_RB</t>
+        </is>
+      </c>
+      <c r="C92" t="n">
+        <v>1</v>
+      </c>
+      <c r="D92" t="n">
+        <v>565</v>
+      </c>
+      <c r="E92" t="n">
+        <v>565</v>
+      </c>
+      <c r="F92" t="n">
+        <v>565</v>
+      </c>
+      <c r="G92" t="n">
+        <v>565</v>
+      </c>
+    </row>
+    <row r="93">
+      <c r="A93" t="inlineStr">
+        <is>
+          <t>Run_9</t>
+        </is>
+      </c>
+      <c r="B93" t="inlineStr">
+        <is>
+          <t>Track_150</t>
+        </is>
+      </c>
+      <c r="C93" t="n">
+        <v>6</v>
+      </c>
+      <c r="D93" t="n">
+        <v>3429</v>
+      </c>
+      <c r="E93" t="n">
+        <v>645</v>
+      </c>
+      <c r="F93" t="n">
+        <v>541</v>
+      </c>
+      <c r="G93" t="n">
+        <v>571</v>
+      </c>
+    </row>
+    <row r="94">
+      <c r="A94" t="inlineStr">
+        <is>
+          <t>Run_9</t>
+        </is>
+      </c>
+      <c r="B94" t="inlineStr">
+        <is>
+          <t>Track_200</t>
+        </is>
+      </c>
+      <c r="C94" t="n">
+        <v>2</v>
+      </c>
+      <c r="D94" t="n">
+        <v>1187</v>
+      </c>
+      <c r="E94" t="n">
+        <v>619</v>
+      </c>
+      <c r="F94" t="n">
+        <v>568</v>
+      </c>
+      <c r="G94" t="n">
+        <v>593</v>
+      </c>
+    </row>
+    <row r="95">
+      <c r="A95" t="inlineStr">
+        <is>
+          <t>Run_9</t>
+        </is>
+      </c>
+      <c r="B95" t="inlineStr">
+        <is>
+          <t>Track_Accel</t>
+        </is>
+      </c>
+      <c r="C95" t="n">
+        <v>2</v>
+      </c>
+      <c r="D95" t="n">
+        <v>1083</v>
+      </c>
+      <c r="E95" t="n">
+        <v>567</v>
+      </c>
+      <c r="F95" t="n">
+        <v>516</v>
+      </c>
+      <c r="G95" t="n">
+        <v>541</v>
+      </c>
+    </row>
+    <row r="96">
+      <c r="A96" t="inlineStr">
+        <is>
+          <t>Run_9</t>
+        </is>
+      </c>
+      <c r="B96" t="inlineStr">
+        <is>
+          <t>Track_Decel</t>
+        </is>
+      </c>
+      <c r="C96" t="n">
+        <v>3</v>
+      </c>
+      <c r="D96" t="n">
+        <v>1831</v>
+      </c>
+      <c r="E96" t="n">
+        <v>645</v>
+      </c>
+      <c r="F96" t="n">
+        <v>567</v>
+      </c>
+      <c r="G96" t="n">
+        <v>610</v>
+      </c>
+    </row>
+    <row r="97">
+      <c r="A97" t="inlineStr">
+        <is>
+          <t>Run_9</t>
+        </is>
+      </c>
+      <c r="B97" t="inlineStr">
+        <is>
+          <t>Track_UTurn_in</t>
+        </is>
+      </c>
+      <c r="C97" t="n">
+        <v>5</v>
+      </c>
+      <c r="D97" t="n">
+        <v>2222</v>
+      </c>
+      <c r="E97" t="n">
+        <v>522</v>
+      </c>
+      <c r="F97" t="n">
+        <v>392</v>
+      </c>
+      <c r="G97" t="n">
+        <v>444</v>
+      </c>
+    </row>
+    <row r="98">
+      <c r="A98" t="inlineStr">
+        <is>
+          <t>Run_9</t>
+        </is>
+      </c>
+      <c r="B98" t="inlineStr">
+        <is>
+          <t>Track_UTurn_out</t>
+        </is>
+      </c>
+      <c r="C98" t="n">
+        <v>2</v>
+      </c>
+      <c r="D98" t="n">
+        <v>885</v>
+      </c>
+      <c r="E98" t="n">
+        <v>445</v>
+      </c>
+      <c r="F98" t="n">
+        <v>440</v>
+      </c>
+      <c r="G98" t="n">
+        <v>442</v>
+      </c>
+    </row>
+    <row r="99">
+      <c r="A99" t="inlineStr">
+        <is>
+          <t>Run_9</t>
+        </is>
+      </c>
+      <c r="B99" t="inlineStr">
+        <is>
+          <t>Turn_F</t>
+        </is>
+      </c>
+      <c r="C99" t="n">
+        <v>7</v>
+      </c>
+      <c r="D99" t="n">
+        <v>1262</v>
+      </c>
+      <c r="E99" t="n">
+        <v>206</v>
+      </c>
+      <c r="F99" t="n">
+        <v>129</v>
+      </c>
+      <c r="G99" t="n">
+        <v>180</v>
+      </c>
+    </row>
+    <row r="100">
+      <c r="A100" t="inlineStr">
+        <is>
+          <t>Run_9</t>
+        </is>
+      </c>
+      <c r="B100" t="inlineStr">
+        <is>
+          <t>Turn_L</t>
+        </is>
+      </c>
+      <c r="C100" t="n">
+        <v>3</v>
+      </c>
+      <c r="D100" t="n">
+        <v>1440</v>
+      </c>
+      <c r="E100" t="n">
+        <v>489</v>
+      </c>
+      <c r="F100" t="n">
+        <v>463</v>
+      </c>
+      <c r="G100" t="n">
+        <v>480</v>
+      </c>
+    </row>
+    <row r="101">
+      <c r="A101" t="inlineStr">
+        <is>
+          <t>Run_9</t>
+        </is>
+      </c>
+      <c r="B101" t="inlineStr">
+        <is>
+          <t>Turn_R</t>
+        </is>
+      </c>
+      <c r="C101" t="n">
+        <v>6</v>
+      </c>
+      <c r="D101" t="n">
+        <v>3006</v>
+      </c>
+      <c r="E101" t="n">
+        <v>514</v>
+      </c>
+      <c r="F101" t="n">
+        <v>488</v>
+      </c>
+      <c r="G101" t="n">
+        <v>501</v>
+      </c>
+    </row>
+    <row r="102">
+      <c r="A102" t="inlineStr">
+        <is>
+          <t>Run_9</t>
+        </is>
+      </c>
+      <c r="B102" t="inlineStr">
+        <is>
+          <t>Turn_B</t>
+        </is>
+      </c>
+      <c r="C102" t="n">
+        <v>2</v>
+      </c>
+      <c r="D102" t="n">
+        <v>2087</v>
+      </c>
+      <c r="E102" t="n">
+        <v>1110</v>
+      </c>
+      <c r="F102" t="n">
+        <v>977</v>
+      </c>
+      <c r="G102" t="n">
+        <v>1043</v>
+      </c>
+    </row>
+    <row r="103">
+      <c r="A103" t="inlineStr">
+        <is>
+          <t>Run_9</t>
+        </is>
+      </c>
+      <c r="B103" t="inlineStr">
+        <is>
+          <t>Turn_T</t>
+        </is>
+      </c>
+      <c r="C103" t="n">
+        <v>2</v>
+      </c>
+      <c r="D103" t="n">
+        <v>1574</v>
+      </c>
+      <c r="E103" t="n">
+        <v>854</v>
+      </c>
+      <c r="F103" t="n">
+        <v>720</v>
+      </c>
+      <c r="G103" t="n">
+        <v>787</v>
+      </c>
+    </row>
+    <row r="104">
+      <c r="A104" t="inlineStr">
+        <is>
+          <t>Run_9</t>
+        </is>
+      </c>
+      <c r="B104" t="inlineStr">
+        <is>
+          <t>Turn_LB</t>
+        </is>
+      </c>
+      <c r="C104" t="n">
+        <v>1</v>
+      </c>
+      <c r="D104" t="n">
+        <v>438</v>
+      </c>
+      <c r="E104" t="n">
+        <v>438</v>
+      </c>
+      <c r="F104" t="n">
+        <v>438</v>
+      </c>
+      <c r="G104" t="n">
+        <v>438</v>
+      </c>
+    </row>
+    <row r="105">
+      <c r="A105" t="inlineStr">
+        <is>
+          <t>Run_9</t>
+        </is>
+      </c>
+      <c r="B105" t="inlineStr">
+        <is>
+          <t>Turn_RB</t>
+        </is>
+      </c>
+      <c r="C105" t="n">
+        <v>1</v>
+      </c>
+      <c r="D105" t="n">
+        <v>540</v>
+      </c>
+      <c r="E105" t="n">
+        <v>540</v>
+      </c>
+      <c r="F105" t="n">
+        <v>540</v>
+      </c>
+      <c r="G105" t="n">
+        <v>540</v>
+      </c>
+    </row>
+    <row r="106">
+      <c r="A106" t="inlineStr">
+        <is>
           <t>Run_10</t>
         </is>
       </c>
-      <c r="B81" t="inlineStr">
+      <c r="B106" t="inlineStr">
+        <is>
+          <t>Track_150</t>
+        </is>
+      </c>
+      <c r="C106" t="n">
+        <v>6</v>
+      </c>
+      <c r="D106" t="n">
+        <v>3507</v>
+      </c>
+      <c r="E106" t="n">
+        <v>645</v>
+      </c>
+      <c r="F106" t="n">
+        <v>516</v>
+      </c>
+      <c r="G106" t="n">
+        <v>584</v>
+      </c>
+    </row>
+    <row r="107">
+      <c r="A107" t="inlineStr">
+        <is>
+          <t>Run_10</t>
+        </is>
+      </c>
+      <c r="B107" t="inlineStr">
+        <is>
+          <t>Track_200</t>
+        </is>
+      </c>
+      <c r="C107" t="n">
+        <v>1</v>
+      </c>
+      <c r="D107" t="n">
+        <v>593</v>
+      </c>
+      <c r="E107" t="n">
+        <v>593</v>
+      </c>
+      <c r="F107" t="n">
+        <v>593</v>
+      </c>
+      <c r="G107" t="n">
+        <v>593</v>
+      </c>
+    </row>
+    <row r="108">
+      <c r="A108" t="inlineStr">
+        <is>
+          <t>Run_10</t>
+        </is>
+      </c>
+      <c r="B108" t="inlineStr">
+        <is>
+          <t>Track_Accel</t>
+        </is>
+      </c>
+      <c r="C108" t="n">
+        <v>1</v>
+      </c>
+      <c r="D108" t="n">
+        <v>413</v>
+      </c>
+      <c r="E108" t="n">
+        <v>413</v>
+      </c>
+      <c r="F108" t="n">
+        <v>413</v>
+      </c>
+      <c r="G108" t="n">
+        <v>413</v>
+      </c>
+    </row>
+    <row r="109">
+      <c r="A109" t="inlineStr">
+        <is>
+          <t>Run_10</t>
+        </is>
+      </c>
+      <c r="B109" t="inlineStr">
+        <is>
+          <t>Track_Decel</t>
+        </is>
+      </c>
+      <c r="C109" t="n">
+        <v>2</v>
+      </c>
+      <c r="D109" t="n">
+        <v>1288</v>
+      </c>
+      <c r="E109" t="n">
+        <v>696</v>
+      </c>
+      <c r="F109" t="n">
+        <v>592</v>
+      </c>
+      <c r="G109" t="n">
+        <v>644</v>
+      </c>
+    </row>
+    <row r="110">
+      <c r="A110" t="inlineStr">
+        <is>
+          <t>Run_10</t>
+        </is>
+      </c>
+      <c r="B110" t="inlineStr">
+        <is>
+          <t>Track_UTurn_in</t>
+        </is>
+      </c>
+      <c r="C110" t="n">
+        <v>5</v>
+      </c>
+      <c r="D110" t="n">
+        <v>2198</v>
+      </c>
+      <c r="E110" t="n">
+        <v>625</v>
+      </c>
+      <c r="F110" t="n">
+        <v>316</v>
+      </c>
+      <c r="G110" t="n">
+        <v>439</v>
+      </c>
+    </row>
+    <row r="111">
+      <c r="A111" t="inlineStr">
+        <is>
+          <t>Run_10</t>
+        </is>
+      </c>
+      <c r="B111" t="inlineStr">
+        <is>
+          <t>Track_UTurn_out</t>
+        </is>
+      </c>
+      <c r="C111" t="n">
+        <v>2</v>
+      </c>
+      <c r="D111" t="n">
+        <v>943</v>
+      </c>
+      <c r="E111" t="n">
+        <v>497</v>
+      </c>
+      <c r="F111" t="n">
+        <v>446</v>
+      </c>
+      <c r="G111" t="n">
+        <v>471</v>
+      </c>
+    </row>
+    <row r="112">
+      <c r="A112" t="inlineStr">
+        <is>
+          <t>Run_10</t>
+        </is>
+      </c>
+      <c r="B112" t="inlineStr">
+        <is>
+          <t>Turn_F</t>
+        </is>
+      </c>
+      <c r="C112" t="n">
+        <v>5</v>
+      </c>
+      <c r="D112" t="n">
+        <v>876</v>
+      </c>
+      <c r="E112" t="n">
+        <v>206</v>
+      </c>
+      <c r="F112" t="n">
+        <v>155</v>
+      </c>
+      <c r="G112" t="n">
+        <v>175</v>
+      </c>
+    </row>
+    <row r="113">
+      <c r="A113" t="inlineStr">
+        <is>
+          <t>Run_10</t>
+        </is>
+      </c>
+      <c r="B113" t="inlineStr">
+        <is>
+          <t>Turn_L</t>
+        </is>
+      </c>
+      <c r="C113" t="n">
+        <v>4</v>
+      </c>
+      <c r="D113" t="n">
+        <v>2184</v>
+      </c>
+      <c r="E113" t="n">
+        <v>642</v>
+      </c>
+      <c r="F113" t="n">
+        <v>411</v>
+      </c>
+      <c r="G113" t="n">
+        <v>546</v>
+      </c>
+    </row>
+    <row r="114">
+      <c r="A114" t="inlineStr">
+        <is>
+          <t>Run_10</t>
+        </is>
+      </c>
+      <c r="B114" t="inlineStr">
+        <is>
+          <t>Turn_R</t>
+        </is>
+      </c>
+      <c r="C114" t="n">
+        <v>4</v>
+      </c>
+      <c r="D114" t="n">
+        <v>2031</v>
+      </c>
+      <c r="E114" t="n">
+        <v>565</v>
+      </c>
+      <c r="F114" t="n">
+        <v>437</v>
+      </c>
+      <c r="G114" t="n">
+        <v>507</v>
+      </c>
+    </row>
+    <row r="115">
+      <c r="A115" t="inlineStr">
+        <is>
+          <t>Run_10</t>
+        </is>
+      </c>
+      <c r="B115" t="inlineStr">
+        <is>
+          <t>Turn_B</t>
+        </is>
+      </c>
+      <c r="C115" t="n">
+        <v>2</v>
+      </c>
+      <c r="D115" t="n">
+        <v>2376</v>
+      </c>
+      <c r="E115" t="n">
+        <v>1343</v>
+      </c>
+      <c r="F115" t="n">
+        <v>1033</v>
+      </c>
+      <c r="G115" t="n">
+        <v>1188</v>
+      </c>
+    </row>
+    <row r="116">
+      <c r="A116" t="inlineStr">
+        <is>
+          <t>Run_10</t>
+        </is>
+      </c>
+      <c r="B116" t="inlineStr">
+        <is>
+          <t>Turn_T</t>
+        </is>
+      </c>
+      <c r="C116" t="n">
+        <v>2</v>
+      </c>
+      <c r="D116" t="n">
+        <v>1644</v>
+      </c>
+      <c r="E116" t="n">
+        <v>848</v>
+      </c>
+      <c r="F116" t="n">
+        <v>796</v>
+      </c>
+      <c r="G116" t="n">
+        <v>822</v>
+      </c>
+    </row>
+    <row r="117">
+      <c r="A117" t="inlineStr">
+        <is>
+          <t>Run_10</t>
+        </is>
+      </c>
+      <c r="B117" t="inlineStr">
         <is>
           <t>Turn_LB</t>
         </is>
       </c>
-      <c r="C81" t="n">
+      <c r="C117" t="n">
+        <v>2</v>
+      </c>
+      <c r="D117" t="n">
+        <v>772</v>
+      </c>
+      <c r="E117" t="n">
+        <v>463</v>
+      </c>
+      <c r="F117" t="n">
+        <v>309</v>
+      </c>
+      <c r="G117" t="n">
+        <v>386</v>
+      </c>
+    </row>
+    <row r="118">
+      <c r="A118" t="inlineStr">
+        <is>
+          <t>Run_11</t>
+        </is>
+      </c>
+      <c r="B118" t="inlineStr">
+        <is>
+          <t>Track_150</t>
+        </is>
+      </c>
+      <c r="C118" t="n">
+        <v>6</v>
+      </c>
+      <c r="D118" t="n">
+        <v>3354</v>
+      </c>
+      <c r="E118" t="n">
+        <v>594</v>
+      </c>
+      <c r="F118" t="n">
+        <v>516</v>
+      </c>
+      <c r="G118" t="n">
+        <v>559</v>
+      </c>
+    </row>
+    <row r="119">
+      <c r="A119" t="inlineStr">
+        <is>
+          <t>Run_11</t>
+        </is>
+      </c>
+      <c r="B119" t="inlineStr">
+        <is>
+          <t>Track_200</t>
+        </is>
+      </c>
+      <c r="C119" t="n">
         <v>1</v>
       </c>
-      <c r="D81" t="n">
+      <c r="D119" t="n">
+        <v>593</v>
+      </c>
+      <c r="E119" t="n">
+        <v>593</v>
+      </c>
+      <c r="F119" t="n">
+        <v>593</v>
+      </c>
+      <c r="G119" t="n">
+        <v>593</v>
+      </c>
+    </row>
+    <row r="120">
+      <c r="A120" t="inlineStr">
+        <is>
+          <t>Run_11</t>
+        </is>
+      </c>
+      <c r="B120" t="inlineStr">
+        <is>
+          <t>Track_Accel</t>
+        </is>
+      </c>
+      <c r="C120" t="n">
+        <v>2</v>
+      </c>
+      <c r="D120" t="n">
+        <v>1056</v>
+      </c>
+      <c r="E120" t="n">
+        <v>541</v>
+      </c>
+      <c r="F120" t="n">
+        <v>515</v>
+      </c>
+      <c r="G120" t="n">
+        <v>528</v>
+      </c>
+    </row>
+    <row r="121">
+      <c r="A121" t="inlineStr">
+        <is>
+          <t>Run_11</t>
+        </is>
+      </c>
+      <c r="B121" t="inlineStr">
+        <is>
+          <t>Track_Decel</t>
+        </is>
+      </c>
+      <c r="C121" t="n">
+        <v>3</v>
+      </c>
+      <c r="D121" t="n">
+        <v>1753</v>
+      </c>
+      <c r="E121" t="n">
+        <v>645</v>
+      </c>
+      <c r="F121" t="n">
+        <v>491</v>
+      </c>
+      <c r="G121" t="n">
+        <v>584</v>
+      </c>
+    </row>
+    <row r="122">
+      <c r="A122" t="inlineStr">
+        <is>
+          <t>Run_11</t>
+        </is>
+      </c>
+      <c r="B122" t="inlineStr">
+        <is>
+          <t>Track_UTurn_in</t>
+        </is>
+      </c>
+      <c r="C122" t="n">
+        <v>5</v>
+      </c>
+      <c r="D122" t="n">
+        <v>2221</v>
+      </c>
+      <c r="E122" t="n">
+        <v>546</v>
+      </c>
+      <c r="F122" t="n">
+        <v>368</v>
+      </c>
+      <c r="G122" t="n">
+        <v>444</v>
+      </c>
+    </row>
+    <row r="123">
+      <c r="A123" t="inlineStr">
+        <is>
+          <t>Run_11</t>
+        </is>
+      </c>
+      <c r="B123" t="inlineStr">
+        <is>
+          <t>Track_UTurn_out</t>
+        </is>
+      </c>
+      <c r="C123" t="n">
+        <v>2</v>
+      </c>
+      <c r="D123" t="n">
+        <v>936</v>
+      </c>
+      <c r="E123" t="n">
+        <v>497</v>
+      </c>
+      <c r="F123" t="n">
+        <v>439</v>
+      </c>
+      <c r="G123" t="n">
+        <v>468</v>
+      </c>
+    </row>
+    <row r="124">
+      <c r="A124" t="inlineStr">
+        <is>
+          <t>Run_11</t>
+        </is>
+      </c>
+      <c r="B124" t="inlineStr">
+        <is>
+          <t>Turn_F</t>
+        </is>
+      </c>
+      <c r="C124" t="n">
+        <v>6</v>
+      </c>
+      <c r="D124" t="n">
+        <v>1136</v>
+      </c>
+      <c r="E124" t="n">
+        <v>258</v>
+      </c>
+      <c r="F124" t="n">
+        <v>155</v>
+      </c>
+      <c r="G124" t="n">
+        <v>189</v>
+      </c>
+    </row>
+    <row r="125">
+      <c r="A125" t="inlineStr">
+        <is>
+          <t>Run_11</t>
+        </is>
+      </c>
+      <c r="B125" t="inlineStr">
+        <is>
+          <t>Turn_L</t>
+        </is>
+      </c>
+      <c r="C125" t="n">
+        <v>3</v>
+      </c>
+      <c r="D125" t="n">
+        <v>1491</v>
+      </c>
+      <c r="E125" t="n">
+        <v>513</v>
+      </c>
+      <c r="F125" t="n">
+        <v>489</v>
+      </c>
+      <c r="G125" t="n">
+        <v>497</v>
+      </c>
+    </row>
+    <row r="126">
+      <c r="A126" t="inlineStr">
+        <is>
+          <t>Run_11</t>
+        </is>
+      </c>
+      <c r="B126" t="inlineStr">
+        <is>
+          <t>Turn_R</t>
+        </is>
+      </c>
+      <c r="C126" t="n">
+        <v>6</v>
+      </c>
+      <c r="D126" t="n">
+        <v>3134</v>
+      </c>
+      <c r="E126" t="n">
+        <v>540</v>
+      </c>
+      <c r="F126" t="n">
+        <v>488</v>
+      </c>
+      <c r="G126" t="n">
+        <v>522</v>
+      </c>
+    </row>
+    <row r="127">
+      <c r="A127" t="inlineStr">
+        <is>
+          <t>Run_11</t>
+        </is>
+      </c>
+      <c r="B127" t="inlineStr">
+        <is>
+          <t>Turn_B</t>
+        </is>
+      </c>
+      <c r="C127" t="n">
+        <v>2</v>
+      </c>
+      <c r="D127" t="n">
+        <v>1965</v>
+      </c>
+      <c r="E127" t="n">
+        <v>1009</v>
+      </c>
+      <c r="F127" t="n">
+        <v>956</v>
+      </c>
+      <c r="G127" t="n">
+        <v>982</v>
+      </c>
+    </row>
+    <row r="128">
+      <c r="A128" t="inlineStr">
+        <is>
+          <t>Run_11</t>
+        </is>
+      </c>
+      <c r="B128" t="inlineStr">
+        <is>
+          <t>Turn_T</t>
+        </is>
+      </c>
+      <c r="C128" t="n">
+        <v>2</v>
+      </c>
+      <c r="D128" t="n">
+        <v>1499</v>
+      </c>
+      <c r="E128" t="n">
+        <v>754</v>
+      </c>
+      <c r="F128" t="n">
+        <v>745</v>
+      </c>
+      <c r="G128" t="n">
+        <v>749</v>
+      </c>
+    </row>
+    <row r="129">
+      <c r="A129" t="inlineStr">
+        <is>
+          <t>Run_11</t>
+        </is>
+      </c>
+      <c r="B129" t="inlineStr">
+        <is>
+          <t>Turn_LB</t>
+        </is>
+      </c>
+      <c r="C129" t="n">
+        <v>1</v>
+      </c>
+      <c r="D129" t="n">
         <v>462</v>
       </c>
-      <c r="E81" t="n">
+      <c r="E129" t="n">
         <v>462</v>
       </c>
-      <c r="F81" t="n">
+      <c r="F129" t="n">
         <v>462</v>
       </c>
-      <c r="G81" t="n">
+      <c r="G129" t="n">
         <v>462</v>
+      </c>
+    </row>
+    <row r="130">
+      <c r="A130" t="inlineStr">
+        <is>
+          <t>Run_11</t>
+        </is>
+      </c>
+      <c r="B130" t="inlineStr">
+        <is>
+          <t>Turn_RB</t>
+        </is>
+      </c>
+      <c r="C130" t="n">
+        <v>1</v>
+      </c>
+      <c r="D130" t="n">
+        <v>489</v>
+      </c>
+      <c r="E130" t="n">
+        <v>489</v>
+      </c>
+      <c r="F130" t="n">
+        <v>489</v>
+      </c>
+      <c r="G130" t="n">
+        <v>489</v>
+      </c>
+    </row>
+    <row r="131">
+      <c r="A131" t="inlineStr">
+        <is>
+          <t>Run_12</t>
+        </is>
+      </c>
+      <c r="B131" t="inlineStr">
+        <is>
+          <t>Track_150</t>
+        </is>
+      </c>
+      <c r="C131" t="n">
+        <v>4</v>
+      </c>
+      <c r="D131" t="n">
+        <v>2322</v>
+      </c>
+      <c r="E131" t="n">
+        <v>618</v>
+      </c>
+      <c r="F131" t="n">
+        <v>543</v>
+      </c>
+      <c r="G131" t="n">
+        <v>580</v>
+      </c>
+    </row>
+    <row r="132">
+      <c r="A132" t="inlineStr">
+        <is>
+          <t>Run_12</t>
+        </is>
+      </c>
+      <c r="B132" t="inlineStr">
+        <is>
+          <t>Track_200</t>
+        </is>
+      </c>
+      <c r="C132" t="n">
+        <v>2</v>
+      </c>
+      <c r="D132" t="n">
+        <v>1109</v>
+      </c>
+      <c r="E132" t="n">
+        <v>593</v>
+      </c>
+      <c r="F132" t="n">
+        <v>516</v>
+      </c>
+      <c r="G132" t="n">
+        <v>554</v>
+      </c>
+    </row>
+    <row r="133">
+      <c r="A133" t="inlineStr">
+        <is>
+          <t>Run_12</t>
+        </is>
+      </c>
+      <c r="B133" t="inlineStr">
+        <is>
+          <t>Track_Accel</t>
+        </is>
+      </c>
+      <c r="C133" t="n">
+        <v>2</v>
+      </c>
+      <c r="D133" t="n">
+        <v>1162</v>
+      </c>
+      <c r="E133" t="n">
+        <v>620</v>
+      </c>
+      <c r="F133" t="n">
+        <v>542</v>
+      </c>
+      <c r="G133" t="n">
+        <v>581</v>
+      </c>
+    </row>
+    <row r="134">
+      <c r="A134" t="inlineStr">
+        <is>
+          <t>Run_12</t>
+        </is>
+      </c>
+      <c r="B134" t="inlineStr">
+        <is>
+          <t>Track_Decel</t>
+        </is>
+      </c>
+      <c r="C134" t="n">
+        <v>2</v>
+      </c>
+      <c r="D134" t="n">
+        <v>1239</v>
+      </c>
+      <c r="E134" t="n">
+        <v>645</v>
+      </c>
+      <c r="F134" t="n">
+        <v>594</v>
+      </c>
+      <c r="G134" t="n">
+        <v>619</v>
+      </c>
+    </row>
+    <row r="135">
+      <c r="A135" t="inlineStr">
+        <is>
+          <t>Run_12</t>
+        </is>
+      </c>
+      <c r="B135" t="inlineStr">
+        <is>
+          <t>Track_UTurn_in</t>
+        </is>
+      </c>
+      <c r="C135" t="n">
+        <v>5</v>
+      </c>
+      <c r="D135" t="n">
+        <v>2300</v>
+      </c>
+      <c r="E135" t="n">
+        <v>573</v>
+      </c>
+      <c r="F135" t="n">
+        <v>367</v>
+      </c>
+      <c r="G135" t="n">
+        <v>460</v>
+      </c>
+    </row>
+    <row r="136">
+      <c r="A136" t="inlineStr">
+        <is>
+          <t>Run_12</t>
+        </is>
+      </c>
+      <c r="B136" t="inlineStr">
+        <is>
+          <t>Track_UTurn_out</t>
+        </is>
+      </c>
+      <c r="C136" t="n">
+        <v>2</v>
+      </c>
+      <c r="D136" t="n">
+        <v>891</v>
+      </c>
+      <c r="E136" t="n">
+        <v>446</v>
+      </c>
+      <c r="F136" t="n">
+        <v>445</v>
+      </c>
+      <c r="G136" t="n">
+        <v>445</v>
+      </c>
+    </row>
+    <row r="137">
+      <c r="A137" t="inlineStr">
+        <is>
+          <t>Run_12</t>
+        </is>
+      </c>
+      <c r="B137" t="inlineStr">
+        <is>
+          <t>Turn_F</t>
+        </is>
+      </c>
+      <c r="C137" t="n">
+        <v>7</v>
+      </c>
+      <c r="D137" t="n">
+        <v>1415</v>
+      </c>
+      <c r="E137" t="n">
+        <v>257</v>
+      </c>
+      <c r="F137" t="n">
+        <v>155</v>
+      </c>
+      <c r="G137" t="n">
+        <v>202</v>
+      </c>
+    </row>
+    <row r="138">
+      <c r="A138" t="inlineStr">
+        <is>
+          <t>Run_12</t>
+        </is>
+      </c>
+      <c r="B138" t="inlineStr">
+        <is>
+          <t>Turn_L</t>
+        </is>
+      </c>
+      <c r="C138" t="n">
+        <v>3</v>
+      </c>
+      <c r="D138" t="n">
+        <v>1362</v>
+      </c>
+      <c r="E138" t="n">
+        <v>489</v>
+      </c>
+      <c r="F138" t="n">
+        <v>386</v>
+      </c>
+      <c r="G138" t="n">
+        <v>454</v>
+      </c>
+    </row>
+    <row r="139">
+      <c r="A139" t="inlineStr">
+        <is>
+          <t>Run_12</t>
+        </is>
+      </c>
+      <c r="B139" t="inlineStr">
+        <is>
+          <t>Turn_R</t>
+        </is>
+      </c>
+      <c r="C139" t="n">
+        <v>3</v>
+      </c>
+      <c r="D139" t="n">
+        <v>1540</v>
+      </c>
+      <c r="E139" t="n">
+        <v>564</v>
+      </c>
+      <c r="F139" t="n">
+        <v>462</v>
+      </c>
+      <c r="G139" t="n">
+        <v>513</v>
+      </c>
+    </row>
+    <row r="140">
+      <c r="A140" t="inlineStr">
+        <is>
+          <t>Run_12</t>
+        </is>
+      </c>
+      <c r="B140" t="inlineStr">
+        <is>
+          <t>Turn_B</t>
+        </is>
+      </c>
+      <c r="C140" t="n">
+        <v>2</v>
+      </c>
+      <c r="D140" t="n">
+        <v>1990</v>
+      </c>
+      <c r="E140" t="n">
+        <v>1007</v>
+      </c>
+      <c r="F140" t="n">
+        <v>983</v>
+      </c>
+      <c r="G140" t="n">
+        <v>995</v>
+      </c>
+    </row>
+    <row r="141">
+      <c r="A141" t="inlineStr">
+        <is>
+          <t>Run_12</t>
+        </is>
+      </c>
+      <c r="B141" t="inlineStr">
+        <is>
+          <t>Turn_T</t>
+        </is>
+      </c>
+      <c r="C141" t="n">
+        <v>2</v>
+      </c>
+      <c r="D141" t="n">
+        <v>1671</v>
+      </c>
+      <c r="E141" t="n">
+        <v>874</v>
+      </c>
+      <c r="F141" t="n">
+        <v>797</v>
+      </c>
+      <c r="G141" t="n">
+        <v>835</v>
+      </c>
+    </row>
+    <row r="142">
+      <c r="A142" t="inlineStr">
+        <is>
+          <t>Run_12</t>
+        </is>
+      </c>
+      <c r="B142" t="inlineStr">
+        <is>
+          <t>Turn_LB</t>
+        </is>
+      </c>
+      <c r="C142" t="n">
+        <v>1</v>
+      </c>
+      <c r="D142" t="n">
+        <v>489</v>
+      </c>
+      <c r="E142" t="n">
+        <v>489</v>
+      </c>
+      <c r="F142" t="n">
+        <v>489</v>
+      </c>
+      <c r="G142" t="n">
+        <v>489</v>
+      </c>
+    </row>
+    <row r="143">
+      <c r="A143" t="inlineStr">
+        <is>
+          <t>Run_12</t>
+        </is>
+      </c>
+      <c r="B143" t="inlineStr">
+        <is>
+          <t>Turn_RB</t>
+        </is>
+      </c>
+      <c r="C143" t="n">
+        <v>1</v>
+      </c>
+      <c r="D143" t="n">
+        <v>487</v>
+      </c>
+      <c r="E143" t="n">
+        <v>487</v>
+      </c>
+      <c r="F143" t="n">
+        <v>487</v>
+      </c>
+      <c r="G143" t="n">
+        <v>487</v>
+      </c>
+    </row>
+    <row r="144">
+      <c r="A144" t="inlineStr">
+        <is>
+          <t>Run_13</t>
+        </is>
+      </c>
+      <c r="B144" t="inlineStr">
+        <is>
+          <t>Track_150</t>
+        </is>
+      </c>
+      <c r="C144" t="n">
+        <v>6</v>
+      </c>
+      <c r="D144" t="n">
+        <v>3454</v>
+      </c>
+      <c r="E144" t="n">
+        <v>619</v>
+      </c>
+      <c r="F144" t="n">
+        <v>542</v>
+      </c>
+      <c r="G144" t="n">
+        <v>575</v>
+      </c>
+    </row>
+    <row r="145">
+      <c r="A145" t="inlineStr">
+        <is>
+          <t>Run_13</t>
+        </is>
+      </c>
+      <c r="B145" t="inlineStr">
+        <is>
+          <t>Track_200</t>
+        </is>
+      </c>
+      <c r="C145" t="n">
+        <v>2</v>
+      </c>
+      <c r="D145" t="n">
+        <v>1161</v>
+      </c>
+      <c r="E145" t="n">
+        <v>593</v>
+      </c>
+      <c r="F145" t="n">
+        <v>568</v>
+      </c>
+      <c r="G145" t="n">
+        <v>580</v>
+      </c>
+    </row>
+    <row r="146">
+      <c r="A146" t="inlineStr">
+        <is>
+          <t>Run_13</t>
+        </is>
+      </c>
+      <c r="B146" t="inlineStr">
+        <is>
+          <t>Track_Accel</t>
+        </is>
+      </c>
+      <c r="C146" t="n">
+        <v>2</v>
+      </c>
+      <c r="D146" t="n">
+        <v>1058</v>
+      </c>
+      <c r="E146" t="n">
+        <v>568</v>
+      </c>
+      <c r="F146" t="n">
+        <v>490</v>
+      </c>
+      <c r="G146" t="n">
+        <v>529</v>
+      </c>
+    </row>
+    <row r="147">
+      <c r="A147" t="inlineStr">
+        <is>
+          <t>Run_13</t>
+        </is>
+      </c>
+      <c r="B147" t="inlineStr">
+        <is>
+          <t>Track_Decel</t>
+        </is>
+      </c>
+      <c r="C147" t="n">
+        <v>3</v>
+      </c>
+      <c r="D147" t="n">
+        <v>1855</v>
+      </c>
+      <c r="E147" t="n">
+        <v>644</v>
+      </c>
+      <c r="F147" t="n">
+        <v>592</v>
+      </c>
+      <c r="G147" t="n">
+        <v>618</v>
+      </c>
+    </row>
+    <row r="148">
+      <c r="A148" t="inlineStr">
+        <is>
+          <t>Run_13</t>
+        </is>
+      </c>
+      <c r="B148" t="inlineStr">
+        <is>
+          <t>Track_UTurn_in</t>
+        </is>
+      </c>
+      <c r="C148" t="n">
+        <v>5</v>
+      </c>
+      <c r="D148" t="n">
+        <v>2324</v>
+      </c>
+      <c r="E148" t="n">
+        <v>572</v>
+      </c>
+      <c r="F148" t="n">
+        <v>393</v>
+      </c>
+      <c r="G148" t="n">
+        <v>464</v>
+      </c>
+    </row>
+    <row r="149">
+      <c r="A149" t="inlineStr">
+        <is>
+          <t>Run_13</t>
+        </is>
+      </c>
+      <c r="B149" t="inlineStr">
+        <is>
+          <t>Track_UTurn_out</t>
+        </is>
+      </c>
+      <c r="C149" t="n">
+        <v>2</v>
+      </c>
+      <c r="D149" t="n">
+        <v>909</v>
+      </c>
+      <c r="E149" t="n">
+        <v>470</v>
+      </c>
+      <c r="F149" t="n">
+        <v>439</v>
+      </c>
+      <c r="G149" t="n">
+        <v>454</v>
+      </c>
+    </row>
+    <row r="150">
+      <c r="A150" t="inlineStr">
+        <is>
+          <t>Run_13</t>
+        </is>
+      </c>
+      <c r="B150" t="inlineStr">
+        <is>
+          <t>Turn_F</t>
+        </is>
+      </c>
+      <c r="C150" t="n">
+        <v>7</v>
+      </c>
+      <c r="D150" t="n">
+        <v>1266</v>
+      </c>
+      <c r="E150" t="n">
+        <v>233</v>
+      </c>
+      <c r="F150" t="n">
+        <v>130</v>
+      </c>
+      <c r="G150" t="n">
+        <v>180</v>
+      </c>
+    </row>
+    <row r="151">
+      <c r="A151" t="inlineStr">
+        <is>
+          <t>Run_13</t>
+        </is>
+      </c>
+      <c r="B151" t="inlineStr">
+        <is>
+          <t>Turn_L</t>
+        </is>
+      </c>
+      <c r="C151" t="n">
+        <v>5</v>
+      </c>
+      <c r="D151" t="n">
+        <v>2595</v>
+      </c>
+      <c r="E151" t="n">
+        <v>591</v>
+      </c>
+      <c r="F151" t="n">
+        <v>487</v>
+      </c>
+      <c r="G151" t="n">
+        <v>519</v>
+      </c>
+    </row>
+    <row r="152">
+      <c r="A152" t="inlineStr">
+        <is>
+          <t>Run_13</t>
+        </is>
+      </c>
+      <c r="B152" t="inlineStr">
+        <is>
+          <t>Turn_R</t>
+        </is>
+      </c>
+      <c r="C152" t="n">
+        <v>4</v>
+      </c>
+      <c r="D152" t="n">
+        <v>1978</v>
+      </c>
+      <c r="E152" t="n">
+        <v>539</v>
+      </c>
+      <c r="F152" t="n">
+        <v>462</v>
+      </c>
+      <c r="G152" t="n">
+        <v>494</v>
+      </c>
+    </row>
+    <row r="153">
+      <c r="A153" t="inlineStr">
+        <is>
+          <t>Run_13</t>
+        </is>
+      </c>
+      <c r="B153" t="inlineStr">
+        <is>
+          <t>Turn_B</t>
+        </is>
+      </c>
+      <c r="C153" t="n">
+        <v>2</v>
+      </c>
+      <c r="D153" t="n">
+        <v>2246</v>
+      </c>
+      <c r="E153" t="n">
+        <v>1213</v>
+      </c>
+      <c r="F153" t="n">
+        <v>1033</v>
+      </c>
+      <c r="G153" t="n">
+        <v>1123</v>
+      </c>
+    </row>
+    <row r="154">
+      <c r="A154" t="inlineStr">
+        <is>
+          <t>Run_13</t>
+        </is>
+      </c>
+      <c r="B154" t="inlineStr">
+        <is>
+          <t>Turn_T</t>
+        </is>
+      </c>
+      <c r="C154" t="n">
+        <v>2</v>
+      </c>
+      <c r="D154" t="n">
+        <v>1523</v>
+      </c>
+      <c r="E154" t="n">
+        <v>797</v>
+      </c>
+      <c r="F154" t="n">
+        <v>726</v>
+      </c>
+      <c r="G154" t="n">
+        <v>761</v>
+      </c>
+    </row>
+    <row r="155">
+      <c r="A155" t="inlineStr">
+        <is>
+          <t>Run_13</t>
+        </is>
+      </c>
+      <c r="B155" t="inlineStr">
+        <is>
+          <t>Turn_LB</t>
+        </is>
+      </c>
+      <c r="C155" t="n">
+        <v>1</v>
+      </c>
+      <c r="D155" t="n">
+        <v>335</v>
+      </c>
+      <c r="E155" t="n">
+        <v>335</v>
+      </c>
+      <c r="F155" t="n">
+        <v>335</v>
+      </c>
+      <c r="G155" t="n">
+        <v>335</v>
+      </c>
+    </row>
+    <row r="156">
+      <c r="A156" t="inlineStr">
+        <is>
+          <t>Run_13</t>
+        </is>
+      </c>
+      <c r="B156" t="inlineStr">
+        <is>
+          <t>Turn_RB</t>
+        </is>
+      </c>
+      <c r="C156" t="n">
+        <v>1</v>
+      </c>
+      <c r="D156" t="n">
+        <v>540</v>
+      </c>
+      <c r="E156" t="n">
+        <v>540</v>
+      </c>
+      <c r="F156" t="n">
+        <v>540</v>
+      </c>
+      <c r="G156" t="n">
+        <v>540</v>
       </c>
     </row>
   </sheetData>
@@ -2672,16 +4697,16 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>7</v>
+        <v>13</v>
       </c>
       <c r="C2" t="n">
-        <v>17</v>
+        <v>51</v>
       </c>
       <c r="D2" t="n">
-        <v>579.71</v>
+        <v>577.02</v>
       </c>
       <c r="E2" t="n">
-        <v>29.27</v>
+        <v>21.96</v>
       </c>
       <c r="F2" t="n">
         <v>671</v>
@@ -2697,22 +4722,22 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>7</v>
+        <v>11</v>
       </c>
       <c r="C3" t="n">
-        <v>8</v>
+        <v>18</v>
       </c>
       <c r="D3" t="n">
-        <v>586.38</v>
+        <v>581.5599999999999</v>
       </c>
       <c r="E3" t="n">
-        <v>288.62</v>
+        <v>19.55</v>
       </c>
       <c r="F3" t="n">
         <v>644</v>
       </c>
       <c r="G3" t="n">
-        <v>0</v>
+        <v>516</v>
       </c>
     </row>
     <row r="4">
@@ -2722,22 +4747,22 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>7</v>
+        <v>13</v>
       </c>
       <c r="C4" t="n">
-        <v>14</v>
+        <v>25</v>
       </c>
       <c r="D4" t="n">
-        <v>530.5700000000001</v>
+        <v>529.28</v>
       </c>
       <c r="E4" t="n">
-        <v>36.08</v>
+        <v>44.75</v>
       </c>
       <c r="F4" t="n">
         <v>645</v>
       </c>
       <c r="G4" t="n">
-        <v>464</v>
+        <v>413</v>
       </c>
     </row>
     <row r="5">
@@ -2747,22 +4772,22 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>7</v>
+        <v>13</v>
       </c>
       <c r="C5" t="n">
-        <v>21</v>
+        <v>37</v>
       </c>
       <c r="D5" t="n">
-        <v>610.33</v>
+        <v>611.1900000000001</v>
       </c>
       <c r="E5" t="n">
-        <v>12.14</v>
+        <v>15.3</v>
       </c>
       <c r="F5" t="n">
-        <v>645</v>
+        <v>696</v>
       </c>
       <c r="G5" t="n">
-        <v>568</v>
+        <v>491</v>
       </c>
     </row>
     <row r="6">
@@ -2772,22 +4797,22 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>7</v>
+        <v>13</v>
       </c>
       <c r="C6" t="n">
-        <v>27</v>
+        <v>57</v>
       </c>
       <c r="D6" t="n">
-        <v>480.33</v>
+        <v>465.93</v>
       </c>
       <c r="E6" t="n">
-        <v>16.21</v>
+        <v>20.16</v>
       </c>
       <c r="F6" t="n">
-        <v>599</v>
+        <v>625</v>
       </c>
       <c r="G6" t="n">
-        <v>391</v>
+        <v>316</v>
       </c>
     </row>
     <row r="7">
@@ -2797,19 +4822,19 @@
         </is>
       </c>
       <c r="B7" t="n">
-        <v>7</v>
+        <v>13</v>
       </c>
       <c r="C7" t="n">
-        <v>14</v>
+        <v>26</v>
       </c>
       <c r="D7" t="n">
-        <v>442.79</v>
+        <v>446.65</v>
       </c>
       <c r="E7" t="n">
-        <v>7.72</v>
+        <v>13.16</v>
       </c>
       <c r="F7" t="n">
-        <v>471</v>
+        <v>497</v>
       </c>
       <c r="G7" t="n">
         <v>412</v>
@@ -2818,176 +4843,176 @@
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>Turn_B</t>
+          <t>Turn_F</t>
         </is>
       </c>
       <c r="B8" t="n">
-        <v>4</v>
+        <v>13</v>
       </c>
       <c r="C8" t="n">
-        <v>6</v>
+        <v>82</v>
       </c>
       <c r="D8" t="n">
-        <v>1016</v>
+        <v>186.9</v>
       </c>
       <c r="E8" t="n">
-        <v>41.81</v>
+        <v>9.09</v>
       </c>
       <c r="F8" t="n">
-        <v>1086</v>
+        <v>258</v>
       </c>
       <c r="G8" t="n">
-        <v>976</v>
+        <v>129</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>Turn_F</t>
+          <t>Turn_L</t>
         </is>
       </c>
       <c r="B9" t="n">
-        <v>7</v>
+        <v>13</v>
       </c>
       <c r="C9" t="n">
-        <v>43</v>
+        <v>32</v>
       </c>
       <c r="D9" t="n">
-        <v>186.7</v>
+        <v>497.09</v>
       </c>
       <c r="E9" t="n">
-        <v>9.199999999999999</v>
+        <v>43.95</v>
       </c>
       <c r="F9" t="n">
-        <v>233</v>
+        <v>642</v>
       </c>
       <c r="G9" t="n">
-        <v>129</v>
+        <v>386</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>Turn_L</t>
+          <t>Turn_R</t>
         </is>
       </c>
       <c r="B10" t="n">
-        <v>7</v>
+        <v>13</v>
       </c>
       <c r="C10" t="n">
-        <v>11</v>
+        <v>56</v>
       </c>
       <c r="D10" t="n">
-        <v>488.18</v>
+        <v>496.45</v>
       </c>
       <c r="E10" t="n">
-        <v>54.87</v>
+        <v>25.56</v>
       </c>
       <c r="F10" t="n">
-        <v>565</v>
+        <v>566</v>
       </c>
       <c r="G10" t="n">
-        <v>411</v>
+        <v>386</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>Turn_LB</t>
+          <t>Turn_T</t>
         </is>
       </c>
       <c r="B11" t="n">
-        <v>4</v>
+        <v>13</v>
       </c>
       <c r="C11" t="n">
-        <v>4</v>
+        <v>26</v>
       </c>
       <c r="D11" t="n">
-        <v>475.25</v>
+        <v>785.23</v>
       </c>
       <c r="E11" t="n">
-        <v>14.73</v>
+        <v>27.4</v>
       </c>
       <c r="F11" t="n">
-        <v>488</v>
+        <v>874</v>
       </c>
       <c r="G11" t="n">
-        <v>462</v>
+        <v>720</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>Turn_R</t>
+          <t>Turn_B</t>
         </is>
       </c>
       <c r="B12" t="n">
-        <v>7</v>
+        <v>10</v>
       </c>
       <c r="C12" t="n">
-        <v>27</v>
+        <v>18</v>
       </c>
       <c r="D12" t="n">
-        <v>490.15</v>
+        <v>1043.17</v>
       </c>
       <c r="E12" t="n">
-        <v>32.98</v>
+        <v>67.81999999999999</v>
       </c>
       <c r="F12" t="n">
-        <v>566</v>
+        <v>1343</v>
       </c>
       <c r="G12" t="n">
-        <v>386</v>
+        <v>956</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>Turn_RB</t>
+          <t>Turn_LB</t>
         </is>
       </c>
       <c r="B13" t="n">
-        <v>2</v>
+        <v>10</v>
       </c>
       <c r="C13" t="n">
-        <v>2</v>
+        <v>11</v>
       </c>
       <c r="D13" t="n">
-        <v>450.5</v>
+        <v>437.18</v>
       </c>
       <c r="E13" t="n">
-        <v>54.45</v>
+        <v>50.75</v>
       </c>
       <c r="F13" t="n">
         <v>489</v>
       </c>
       <c r="G13" t="n">
-        <v>412</v>
+        <v>309</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>Turn_T</t>
+          <t>Turn_RB</t>
         </is>
       </c>
       <c r="B14" t="n">
         <v>7</v>
       </c>
       <c r="C14" t="n">
-        <v>14</v>
+        <v>7</v>
       </c>
       <c r="D14" t="n">
-        <v>782.14</v>
+        <v>503.14</v>
       </c>
       <c r="E14" t="n">
-        <v>22.85</v>
+        <v>50.84</v>
       </c>
       <c r="F14" t="n">
-        <v>854</v>
+        <v>565</v>
       </c>
       <c r="G14" t="n">
-        <v>720</v>
+        <v>412</v>
       </c>
     </row>
   </sheetData>
